--- a/РАБОЧИЙ СТОЛ/ПЕРЕМЕЩЕНИЕ Бердянск - Мариуполь/Бердянск-Мариуполь перемещение ПОКОМ.xlsx
+++ b/РАБОЧИЙ СТОЛ/ПЕРЕМЕЩЕНИЕ Бердянск - Мариуполь/Бердянск-Мариуполь перемещение ПОКОМ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\ПЕРЕМЕЩЕНИЕ Бердянск - Мариуполь\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72FF13A3-F704-45D2-8C29-88956CBFB5F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66059DB0-ABB0-4A83-A2B3-6970D0194A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="400">
   <si>
     <t>Ведомость по товарам на складах</t>
   </si>
@@ -1227,9 +1227,6 @@
   </si>
   <si>
     <t>ШТ</t>
-  </si>
-  <si>
-    <t>нет на остатках (остатки не корректны)</t>
   </si>
 </sst>
 </file>
@@ -1373,36 +1370,6 @@
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1416,6 +1383,36 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -13601,7 +13598,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Q198"/>
+  <dimension ref="A1:P198"/>
   <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="12.75" outlineLevelRow="2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5" style="1" customWidth="1"/>
@@ -13614,7 +13611,6 @@
     <col min="8" max="9" width="14" style="1" customWidth="1"/>
     <col min="11" max="14" width="10.5" style="14"/>
     <col min="15" max="16" width="18.1640625" style="17" customWidth="1"/>
-    <col min="17" max="17" width="36.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -13658,24 +13654,24 @@
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
-      <c r="M5" s="18" t="s">
+      <c r="M5" s="31" t="s">
         <v>396</v>
       </c>
-      <c r="N5" s="19"/>
+      <c r="N5" s="32"/>
     </row>
     <row r="6" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="3"/>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
       <c r="K6" s="15" t="s">
         <v>394</v>
       </c>
@@ -13689,10 +13685,10 @@
         <f>M6</f>
         <v>5</v>
       </c>
-      <c r="O6" s="20" t="s">
+      <c r="O6" s="33" t="s">
         <v>397</v>
       </c>
-      <c r="P6" s="20"/>
+      <c r="P6" s="33"/>
     </row>
     <row r="7" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="K7" s="15"/>
@@ -13712,16 +13708,16 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26" t="s">
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
       <c r="G8" s="4" t="s">
         <v>8</v>
       </c>
@@ -13740,16 +13736,16 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26" t="s">
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
       <c r="G9" s="4" t="s">
         <v>8</v>
       </c>
@@ -13771,48 +13767,48 @@
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23" t="s">
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
       <c r="G10" s="5"/>
       <c r="H10" s="6"/>
       <c r="I10" s="7"/>
       <c r="J10" s="12"/>
     </row>
     <row r="11" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="24" t="s">
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
       <c r="G11" s="5"/>
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
       <c r="J11" s="12"/>
     </row>
     <row r="12" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="22" t="s">
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
       <c r="G12" s="8" t="s">
         <v>12</v>
       </c>
@@ -13852,16 +13848,16 @@
       </c>
     </row>
     <row r="13" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="22" t="s">
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
       <c r="G13" s="8" t="s">
         <v>12</v>
       </c>
@@ -13901,16 +13897,16 @@
       </c>
     </row>
     <row r="14" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="22" t="s">
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
       <c r="G14" s="8" t="s">
         <v>12</v>
       </c>
@@ -13950,16 +13946,16 @@
       </c>
     </row>
     <row r="15" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="22" t="s">
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
       <c r="G15" s="8" t="s">
         <v>12</v>
       </c>
@@ -13999,16 +13995,16 @@
       </c>
     </row>
     <row r="16" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="22" t="s">
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
       <c r="G16" s="8" t="s">
         <v>12</v>
       </c>
@@ -14048,16 +14044,16 @@
       </c>
     </row>
     <row r="17" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="22" t="s">
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
       <c r="G17" s="8" t="s">
         <v>12</v>
       </c>
@@ -14097,16 +14093,16 @@
       </c>
     </row>
     <row r="18" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="22" t="s">
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
       <c r="G18" s="8" t="s">
         <v>12</v>
       </c>
@@ -14146,16 +14142,16 @@
       </c>
     </row>
     <row r="19" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="22" t="s">
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
       <c r="G19" s="8" t="s">
         <v>12</v>
       </c>
@@ -14195,16 +14191,16 @@
       </c>
     </row>
     <row r="20" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="22" t="s">
+      <c r="B20" s="26"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
       <c r="G20" s="8" t="s">
         <v>12</v>
       </c>
@@ -14242,16 +14238,16 @@
       </c>
     </row>
     <row r="21" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="22" t="s">
+      <c r="B21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
       <c r="G21" s="8" t="s">
         <v>12</v>
       </c>
@@ -14291,16 +14287,16 @@
       </c>
     </row>
     <row r="22" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="22" t="s">
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
       <c r="G22" s="8" t="s">
         <v>12</v>
       </c>
@@ -14338,16 +14334,16 @@
       </c>
     </row>
     <row r="23" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="22" t="s">
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
       <c r="G23" s="8" t="s">
         <v>12</v>
       </c>
@@ -14387,16 +14383,16 @@
       </c>
     </row>
     <row r="24" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="22" t="s">
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
       <c r="G24" s="8" t="s">
         <v>12</v>
       </c>
@@ -14436,32 +14432,32 @@
       </c>
     </row>
     <row r="25" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="24" t="s">
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
       <c r="G25" s="5"/>
       <c r="H25" s="7"/>
       <c r="I25" s="11"/>
       <c r="J25" s="12"/>
     </row>
     <row r="26" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A26" s="21" t="s">
+      <c r="A26" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="21"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="22" t="s">
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
       <c r="G26" s="8" t="s">
         <v>13</v>
       </c>
@@ -14501,16 +14497,16 @@
       </c>
     </row>
     <row r="27" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="22" t="s">
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
       <c r="G27" s="8" t="s">
         <v>13</v>
       </c>
@@ -14550,16 +14546,16 @@
       </c>
     </row>
     <row r="28" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="22" t="s">
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
       <c r="G28" s="8" t="s">
         <v>13</v>
       </c>
@@ -14599,16 +14595,16 @@
       </c>
     </row>
     <row r="29" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A29" s="21" t="s">
+      <c r="A29" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="B29" s="21"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="22" t="s">
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
       <c r="G29" s="8" t="s">
         <v>13</v>
       </c>
@@ -14648,16 +14644,16 @@
       </c>
     </row>
     <row r="30" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="B30" s="21"/>
-      <c r="C30" s="21"/>
-      <c r="D30" s="22" t="s">
+      <c r="B30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
       <c r="G30" s="8" t="s">
         <v>13</v>
       </c>
@@ -14697,16 +14693,16 @@
       </c>
     </row>
     <row r="31" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="21"/>
-      <c r="C31" s="21"/>
-      <c r="D31" s="22" t="s">
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
       <c r="G31" s="8" t="s">
         <v>13</v>
       </c>
@@ -14746,16 +14742,16 @@
       </c>
     </row>
     <row r="32" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A32" s="21" t="s">
+      <c r="A32" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="B32" s="21"/>
-      <c r="C32" s="21"/>
-      <c r="D32" s="22" t="s">
+      <c r="B32" s="26"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
       <c r="G32" s="8" t="s">
         <v>13</v>
       </c>
@@ -14793,16 +14789,16 @@
       </c>
     </row>
     <row r="33" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="22" t="s">
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
       <c r="G33" s="8" t="s">
         <v>13</v>
       </c>
@@ -14842,16 +14838,16 @@
       </c>
     </row>
     <row r="34" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A34" s="21" t="s">
+      <c r="A34" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="B34" s="21"/>
-      <c r="C34" s="21"/>
-      <c r="D34" s="22" t="s">
+      <c r="B34" s="26"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
       <c r="G34" s="8" t="s">
         <v>13</v>
       </c>
@@ -14889,16 +14885,16 @@
       </c>
     </row>
     <row r="35" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="B35" s="21"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="22" t="s">
+      <c r="B35" s="26"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
       <c r="G35" s="8" t="s">
         <v>13</v>
       </c>
@@ -14938,16 +14934,16 @@
       </c>
     </row>
     <row r="36" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="B36" s="21"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="22" t="s">
+      <c r="B36" s="26"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="E36" s="22"/>
-      <c r="F36" s="22"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="27"/>
       <c r="G36" s="8" t="s">
         <v>13</v>
       </c>
@@ -14985,16 +14981,16 @@
       </c>
     </row>
     <row r="37" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A37" s="21" t="s">
+      <c r="A37" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="B37" s="21"/>
-      <c r="C37" s="21"/>
-      <c r="D37" s="22" t="s">
+      <c r="B37" s="26"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="E37" s="22"/>
-      <c r="F37" s="22"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="27"/>
       <c r="G37" s="8" t="s">
         <v>13</v>
       </c>
@@ -15032,16 +15028,16 @@
       </c>
     </row>
     <row r="38" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A38" s="21" t="s">
+      <c r="A38" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="B38" s="21"/>
-      <c r="C38" s="21"/>
-      <c r="D38" s="22" t="s">
+      <c r="B38" s="26"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
       <c r="G38" s="8" t="s">
         <v>13</v>
       </c>
@@ -15081,16 +15077,16 @@
       </c>
     </row>
     <row r="39" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A39" s="21" t="s">
+      <c r="A39" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="B39" s="21"/>
-      <c r="C39" s="21"/>
-      <c r="D39" s="22" t="s">
+      <c r="B39" s="26"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="27"/>
       <c r="G39" s="8" t="s">
         <v>13</v>
       </c>
@@ -15130,16 +15126,16 @@
       </c>
     </row>
     <row r="40" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A40" s="21" t="s">
+      <c r="A40" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="22" t="s">
+      <c r="B40" s="26"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="E40" s="22"/>
-      <c r="F40" s="22"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
       <c r="G40" s="8" t="s">
         <v>13</v>
       </c>
@@ -15179,16 +15175,16 @@
       </c>
     </row>
     <row r="41" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A41" s="21" t="s">
+      <c r="A41" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="B41" s="21"/>
-      <c r="C41" s="21"/>
-      <c r="D41" s="22" t="s">
+      <c r="B41" s="26"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="27"/>
       <c r="G41" s="8" t="s">
         <v>13</v>
       </c>
@@ -15226,16 +15222,16 @@
       </c>
     </row>
     <row r="42" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="B42" s="21"/>
-      <c r="C42" s="21"/>
-      <c r="D42" s="22" t="s">
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="E42" s="22"/>
-      <c r="F42" s="22"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="27"/>
       <c r="G42" s="8" t="s">
         <v>13</v>
       </c>
@@ -15273,16 +15269,16 @@
       </c>
     </row>
     <row r="43" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A43" s="21" t="s">
+      <c r="A43" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="B43" s="21"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="22" t="s">
+      <c r="B43" s="26"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="27"/>
       <c r="G43" s="8" t="s">
         <v>13</v>
       </c>
@@ -15320,16 +15316,16 @@
       </c>
     </row>
     <row r="44" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A44" s="21" t="s">
+      <c r="A44" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="B44" s="21"/>
-      <c r="C44" s="21"/>
-      <c r="D44" s="22" t="s">
+      <c r="B44" s="26"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="E44" s="22"/>
-      <c r="F44" s="22"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="27"/>
       <c r="G44" s="8" t="s">
         <v>13</v>
       </c>
@@ -15367,32 +15363,32 @@
       </c>
     </row>
     <row r="45" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="23" t="s">
+      <c r="A45" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="B45" s="23"/>
-      <c r="C45" s="23"/>
-      <c r="D45" s="24" t="s">
+      <c r="B45" s="24"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="E45" s="24"/>
-      <c r="F45" s="24"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="25"/>
       <c r="G45" s="5"/>
       <c r="H45" s="11"/>
       <c r="I45" s="11"/>
       <c r="J45" s="12"/>
     </row>
     <row r="46" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A46" s="21" t="s">
+      <c r="A46" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="B46" s="21"/>
-      <c r="C46" s="21"/>
-      <c r="D46" s="22" t="s">
+      <c r="B46" s="26"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="E46" s="22"/>
-      <c r="F46" s="22"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="27"/>
       <c r="G46" s="8" t="s">
         <v>12</v>
       </c>
@@ -15430,16 +15426,16 @@
       </c>
     </row>
     <row r="47" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A47" s="21" t="s">
+      <c r="A47" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="B47" s="21"/>
-      <c r="C47" s="21"/>
-      <c r="D47" s="22" t="s">
+      <c r="B47" s="26"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="E47" s="22"/>
-      <c r="F47" s="22"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="27"/>
       <c r="G47" s="8" t="s">
         <v>12</v>
       </c>
@@ -15479,16 +15475,16 @@
       </c>
     </row>
     <row r="48" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A48" s="21" t="s">
+      <c r="A48" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="B48" s="21"/>
-      <c r="C48" s="21"/>
-      <c r="D48" s="22" t="s">
+      <c r="B48" s="26"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="E48" s="22"/>
-      <c r="F48" s="22"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="27"/>
       <c r="G48" s="8" t="s">
         <v>12</v>
       </c>
@@ -15528,16 +15524,16 @@
       </c>
     </row>
     <row r="49" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A49" s="21" t="s">
+      <c r="A49" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="B49" s="21"/>
-      <c r="C49" s="21"/>
-      <c r="D49" s="22" t="s">
+      <c r="B49" s="26"/>
+      <c r="C49" s="26"/>
+      <c r="D49" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="E49" s="22"/>
-      <c r="F49" s="22"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
       <c r="G49" s="8" t="s">
         <v>12</v>
       </c>
@@ -15577,16 +15573,16 @@
       </c>
     </row>
     <row r="50" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A50" s="21" t="s">
+      <c r="A50" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="B50" s="21"/>
-      <c r="C50" s="21"/>
-      <c r="D50" s="22" t="s">
+      <c r="B50" s="26"/>
+      <c r="C50" s="26"/>
+      <c r="D50" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="E50" s="22"/>
-      <c r="F50" s="22"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="27"/>
       <c r="G50" s="8" t="s">
         <v>12</v>
       </c>
@@ -15626,16 +15622,16 @@
       </c>
     </row>
     <row r="51" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A51" s="21" t="s">
+      <c r="A51" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="B51" s="21"/>
-      <c r="C51" s="21"/>
-      <c r="D51" s="22" t="s">
+      <c r="B51" s="26"/>
+      <c r="C51" s="26"/>
+      <c r="D51" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="E51" s="22"/>
-      <c r="F51" s="22"/>
+      <c r="E51" s="27"/>
+      <c r="F51" s="27"/>
       <c r="G51" s="8" t="s">
         <v>12</v>
       </c>
@@ -15675,16 +15671,16 @@
       </c>
     </row>
     <row r="52" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A52" s="21" t="s">
+      <c r="A52" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="B52" s="21"/>
-      <c r="C52" s="21"/>
-      <c r="D52" s="22" t="s">
+      <c r="B52" s="26"/>
+      <c r="C52" s="26"/>
+      <c r="D52" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="E52" s="22"/>
-      <c r="F52" s="22"/>
+      <c r="E52" s="27"/>
+      <c r="F52" s="27"/>
       <c r="G52" s="8" t="s">
         <v>12</v>
       </c>
@@ -15722,16 +15718,16 @@
       </c>
     </row>
     <row r="53" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A53" s="21" t="s">
+      <c r="A53" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="B53" s="21"/>
-      <c r="C53" s="21"/>
-      <c r="D53" s="22" t="s">
+      <c r="B53" s="26"/>
+      <c r="C53" s="26"/>
+      <c r="D53" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="E53" s="22"/>
-      <c r="F53" s="22"/>
+      <c r="E53" s="27"/>
+      <c r="F53" s="27"/>
       <c r="G53" s="8" t="s">
         <v>12</v>
       </c>
@@ -15769,32 +15765,32 @@
       </c>
     </row>
     <row r="54" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="23" t="s">
+      <c r="A54" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="23"/>
-      <c r="C54" s="23"/>
-      <c r="D54" s="24" t="s">
+      <c r="B54" s="24"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="E54" s="24"/>
-      <c r="F54" s="24"/>
+      <c r="E54" s="25"/>
+      <c r="F54" s="25"/>
       <c r="G54" s="5"/>
       <c r="H54" s="11"/>
       <c r="I54" s="11"/>
       <c r="J54" s="12"/>
     </row>
     <row r="55" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A55" s="21" t="s">
+      <c r="A55" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="B55" s="21"/>
-      <c r="C55" s="21"/>
-      <c r="D55" s="22" t="s">
+      <c r="B55" s="26"/>
+      <c r="C55" s="26"/>
+      <c r="D55" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="E55" s="22"/>
-      <c r="F55" s="22"/>
+      <c r="E55" s="27"/>
+      <c r="F55" s="27"/>
       <c r="G55" s="8" t="s">
         <v>13</v>
       </c>
@@ -15832,32 +15828,32 @@
       </c>
     </row>
     <row r="56" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="23" t="s">
+      <c r="A56" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="B56" s="23"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="24" t="s">
+      <c r="B56" s="24"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="E56" s="24"/>
-      <c r="F56" s="24"/>
+      <c r="E56" s="25"/>
+      <c r="F56" s="25"/>
       <c r="G56" s="5"/>
       <c r="H56" s="11"/>
       <c r="I56" s="11"/>
       <c r="J56" s="12"/>
     </row>
     <row r="57" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A57" s="21" t="s">
+      <c r="A57" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="B57" s="21"/>
-      <c r="C57" s="21"/>
-      <c r="D57" s="22" t="s">
+      <c r="B57" s="26"/>
+      <c r="C57" s="26"/>
+      <c r="D57" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="E57" s="22"/>
-      <c r="F57" s="22"/>
+      <c r="E57" s="27"/>
+      <c r="F57" s="27"/>
       <c r="G57" s="8" t="s">
         <v>12</v>
       </c>
@@ -15895,32 +15891,32 @@
       </c>
     </row>
     <row r="58" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="23" t="s">
+      <c r="A58" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="B58" s="23"/>
-      <c r="C58" s="23"/>
-      <c r="D58" s="24" t="s">
+      <c r="B58" s="24"/>
+      <c r="C58" s="24"/>
+      <c r="D58" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="E58" s="24"/>
-      <c r="F58" s="24"/>
+      <c r="E58" s="25"/>
+      <c r="F58" s="25"/>
       <c r="G58" s="5"/>
       <c r="H58" s="7"/>
       <c r="I58" s="7"/>
       <c r="J58" s="12"/>
     </row>
     <row r="59" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A59" s="21" t="s">
+      <c r="A59" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="B59" s="21"/>
-      <c r="C59" s="21"/>
-      <c r="D59" s="22" t="s">
+      <c r="B59" s="26"/>
+      <c r="C59" s="26"/>
+      <c r="D59" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="E59" s="22"/>
-      <c r="F59" s="22"/>
+      <c r="E59" s="27"/>
+      <c r="F59" s="27"/>
       <c r="G59" s="8" t="s">
         <v>12</v>
       </c>
@@ -15960,16 +15956,16 @@
       </c>
     </row>
     <row r="60" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A60" s="21" t="s">
+      <c r="A60" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="B60" s="21"/>
-      <c r="C60" s="21"/>
-      <c r="D60" s="22" t="s">
+      <c r="B60" s="26"/>
+      <c r="C60" s="26"/>
+      <c r="D60" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="E60" s="22"/>
-      <c r="F60" s="22"/>
+      <c r="E60" s="27"/>
+      <c r="F60" s="27"/>
       <c r="G60" s="8" t="s">
         <v>12</v>
       </c>
@@ -16009,16 +16005,16 @@
       </c>
     </row>
     <row r="61" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A61" s="21" t="s">
+      <c r="A61" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="B61" s="21"/>
-      <c r="C61" s="21"/>
-      <c r="D61" s="22" t="s">
+      <c r="B61" s="26"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="E61" s="22"/>
-      <c r="F61" s="22"/>
+      <c r="E61" s="27"/>
+      <c r="F61" s="27"/>
       <c r="G61" s="8" t="s">
         <v>12</v>
       </c>
@@ -16058,16 +16054,16 @@
       </c>
     </row>
     <row r="62" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A62" s="21" t="s">
+      <c r="A62" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="B62" s="21"/>
-      <c r="C62" s="21"/>
-      <c r="D62" s="22" t="s">
+      <c r="B62" s="26"/>
+      <c r="C62" s="26"/>
+      <c r="D62" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
+      <c r="E62" s="27"/>
+      <c r="F62" s="27"/>
       <c r="G62" s="8" t="s">
         <v>12</v>
       </c>
@@ -16105,16 +16101,16 @@
       </c>
     </row>
     <row r="63" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A63" s="21" t="s">
+      <c r="A63" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="B63" s="21"/>
-      <c r="C63" s="21"/>
-      <c r="D63" s="22" t="s">
+      <c r="B63" s="26"/>
+      <c r="C63" s="26"/>
+      <c r="D63" s="27" t="s">
         <v>121</v>
       </c>
-      <c r="E63" s="22"/>
-      <c r="F63" s="22"/>
+      <c r="E63" s="27"/>
+      <c r="F63" s="27"/>
       <c r="G63" s="8" t="s">
         <v>12</v>
       </c>
@@ -16154,16 +16150,16 @@
       </c>
     </row>
     <row r="64" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A64" s="21" t="s">
+      <c r="A64" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="B64" s="21"/>
-      <c r="C64" s="21"/>
-      <c r="D64" s="22" t="s">
+      <c r="B64" s="26"/>
+      <c r="C64" s="26"/>
+      <c r="D64" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="E64" s="22"/>
-      <c r="F64" s="22"/>
+      <c r="E64" s="27"/>
+      <c r="F64" s="27"/>
       <c r="G64" s="8" t="s">
         <v>12</v>
       </c>
@@ -16201,16 +16197,16 @@
       </c>
     </row>
     <row r="65" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A65" s="21" t="s">
+      <c r="A65" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="B65" s="21"/>
-      <c r="C65" s="21"/>
-      <c r="D65" s="22" t="s">
+      <c r="B65" s="26"/>
+      <c r="C65" s="26"/>
+      <c r="D65" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22"/>
+      <c r="E65" s="27"/>
+      <c r="F65" s="27"/>
       <c r="G65" s="8" t="s">
         <v>12</v>
       </c>
@@ -16250,16 +16246,16 @@
       </c>
     </row>
     <row r="66" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A66" s="21" t="s">
+      <c r="A66" s="26" t="s">
         <v>126</v>
       </c>
-      <c r="B66" s="21"/>
-      <c r="C66" s="21"/>
-      <c r="D66" s="22" t="s">
+      <c r="B66" s="26"/>
+      <c r="C66" s="26"/>
+      <c r="D66" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="E66" s="22"/>
-      <c r="F66" s="22"/>
+      <c r="E66" s="27"/>
+      <c r="F66" s="27"/>
       <c r="G66" s="8" t="s">
         <v>12</v>
       </c>
@@ -16299,16 +16295,16 @@
       </c>
     </row>
     <row r="67" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A67" s="21" t="s">
+      <c r="A67" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="B67" s="21"/>
-      <c r="C67" s="21"/>
-      <c r="D67" s="22" t="s">
+      <c r="B67" s="26"/>
+      <c r="C67" s="26"/>
+      <c r="D67" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="E67" s="22"/>
-      <c r="F67" s="22"/>
+      <c r="E67" s="27"/>
+      <c r="F67" s="27"/>
       <c r="G67" s="8" t="s">
         <v>12</v>
       </c>
@@ -16348,16 +16344,16 @@
       </c>
     </row>
     <row r="68" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A68" s="21" t="s">
+      <c r="A68" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="B68" s="21"/>
-      <c r="C68" s="21"/>
-      <c r="D68" s="22" t="s">
+      <c r="B68" s="26"/>
+      <c r="C68" s="26"/>
+      <c r="D68" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="E68" s="22"/>
-      <c r="F68" s="22"/>
+      <c r="E68" s="27"/>
+      <c r="F68" s="27"/>
       <c r="G68" s="8" t="s">
         <v>12</v>
       </c>
@@ -16395,16 +16391,16 @@
       </c>
     </row>
     <row r="69" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A69" s="21" t="s">
+      <c r="A69" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="B69" s="21"/>
-      <c r="C69" s="21"/>
-      <c r="D69" s="22" t="s">
+      <c r="B69" s="26"/>
+      <c r="C69" s="26"/>
+      <c r="D69" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="E69" s="22"/>
-      <c r="F69" s="22"/>
+      <c r="E69" s="27"/>
+      <c r="F69" s="27"/>
       <c r="G69" s="8" t="s">
         <v>12</v>
       </c>
@@ -16444,16 +16440,16 @@
       </c>
     </row>
     <row r="70" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A70" s="21" t="s">
+      <c r="A70" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="B70" s="21"/>
-      <c r="C70" s="21"/>
-      <c r="D70" s="22" t="s">
+      <c r="B70" s="26"/>
+      <c r="C70" s="26"/>
+      <c r="D70" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="E70" s="22"/>
-      <c r="F70" s="22"/>
+      <c r="E70" s="27"/>
+      <c r="F70" s="27"/>
       <c r="G70" s="8" t="s">
         <v>12</v>
       </c>
@@ -16493,16 +16489,16 @@
       </c>
     </row>
     <row r="71" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A71" s="21" t="s">
+      <c r="A71" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="B71" s="21"/>
-      <c r="C71" s="21"/>
-      <c r="D71" s="22" t="s">
+      <c r="B71" s="26"/>
+      <c r="C71" s="26"/>
+      <c r="D71" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="E71" s="22"/>
-      <c r="F71" s="22"/>
+      <c r="E71" s="27"/>
+      <c r="F71" s="27"/>
       <c r="G71" s="8" t="s">
         <v>12</v>
       </c>
@@ -16540,16 +16536,16 @@
       </c>
     </row>
     <row r="72" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A72" s="21" t="s">
+      <c r="A72" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="B72" s="21"/>
-      <c r="C72" s="21"/>
-      <c r="D72" s="22" t="s">
+      <c r="B72" s="26"/>
+      <c r="C72" s="26"/>
+      <c r="D72" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="E72" s="22"/>
-      <c r="F72" s="22"/>
+      <c r="E72" s="27"/>
+      <c r="F72" s="27"/>
       <c r="G72" s="8" t="s">
         <v>12</v>
       </c>
@@ -16587,16 +16583,16 @@
       </c>
     </row>
     <row r="73" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A73" s="21" t="s">
+      <c r="A73" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="B73" s="21"/>
-      <c r="C73" s="21"/>
-      <c r="D73" s="22" t="s">
+      <c r="B73" s="26"/>
+      <c r="C73" s="26"/>
+      <c r="D73" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="E73" s="22"/>
-      <c r="F73" s="22"/>
+      <c r="E73" s="27"/>
+      <c r="F73" s="27"/>
       <c r="G73" s="8" t="s">
         <v>12</v>
       </c>
@@ -16634,16 +16630,16 @@
       </c>
     </row>
     <row r="74" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A74" s="21" t="s">
+      <c r="A74" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="B74" s="21"/>
-      <c r="C74" s="21"/>
-      <c r="D74" s="22" t="s">
+      <c r="B74" s="26"/>
+      <c r="C74" s="26"/>
+      <c r="D74" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="E74" s="22"/>
-      <c r="F74" s="22"/>
+      <c r="E74" s="27"/>
+      <c r="F74" s="27"/>
       <c r="G74" s="8" t="s">
         <v>12</v>
       </c>
@@ -16683,16 +16679,16 @@
       </c>
     </row>
     <row r="75" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A75" s="21" t="s">
+      <c r="A75" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="B75" s="21"/>
-      <c r="C75" s="21"/>
-      <c r="D75" s="22" t="s">
+      <c r="B75" s="26"/>
+      <c r="C75" s="26"/>
+      <c r="D75" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="E75" s="22"/>
-      <c r="F75" s="22"/>
+      <c r="E75" s="27"/>
+      <c r="F75" s="27"/>
       <c r="G75" s="8" t="s">
         <v>12</v>
       </c>
@@ -16730,16 +16726,16 @@
       </c>
     </row>
     <row r="76" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A76" s="21" t="s">
+      <c r="A76" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="B76" s="21"/>
-      <c r="C76" s="21"/>
-      <c r="D76" s="22" t="s">
+      <c r="B76" s="26"/>
+      <c r="C76" s="26"/>
+      <c r="D76" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="E76" s="22"/>
-      <c r="F76" s="22"/>
+      <c r="E76" s="27"/>
+      <c r="F76" s="27"/>
       <c r="G76" s="8" t="s">
         <v>12</v>
       </c>
@@ -16779,16 +16775,16 @@
       </c>
     </row>
     <row r="77" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A77" s="21" t="s">
+      <c r="A77" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="B77" s="21"/>
-      <c r="C77" s="21"/>
-      <c r="D77" s="22" t="s">
+      <c r="B77" s="26"/>
+      <c r="C77" s="26"/>
+      <c r="D77" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="E77" s="22"/>
-      <c r="F77" s="22"/>
+      <c r="E77" s="27"/>
+      <c r="F77" s="27"/>
       <c r="G77" s="8" t="s">
         <v>12</v>
       </c>
@@ -16826,16 +16822,16 @@
       </c>
     </row>
     <row r="78" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A78" s="21" t="s">
+      <c r="A78" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="B78" s="21"/>
-      <c r="C78" s="21"/>
-      <c r="D78" s="22" t="s">
+      <c r="B78" s="26"/>
+      <c r="C78" s="26"/>
+      <c r="D78" s="27" t="s">
         <v>151</v>
       </c>
-      <c r="E78" s="22"/>
-      <c r="F78" s="22"/>
+      <c r="E78" s="27"/>
+      <c r="F78" s="27"/>
       <c r="G78" s="8" t="s">
         <v>12</v>
       </c>
@@ -16873,16 +16869,16 @@
       </c>
     </row>
     <row r="79" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A79" s="21" t="s">
+      <c r="A79" s="26" t="s">
         <v>152</v>
       </c>
-      <c r="B79" s="21"/>
-      <c r="C79" s="21"/>
-      <c r="D79" s="22" t="s">
+      <c r="B79" s="26"/>
+      <c r="C79" s="26"/>
+      <c r="D79" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="E79" s="22"/>
-      <c r="F79" s="22"/>
+      <c r="E79" s="27"/>
+      <c r="F79" s="27"/>
       <c r="G79" s="8" t="s">
         <v>12</v>
       </c>
@@ -16920,16 +16916,16 @@
       </c>
     </row>
     <row r="80" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A80" s="21" t="s">
+      <c r="A80" s="26" t="s">
         <v>154</v>
       </c>
-      <c r="B80" s="21"/>
-      <c r="C80" s="21"/>
-      <c r="D80" s="22" t="s">
+      <c r="B80" s="26"/>
+      <c r="C80" s="26"/>
+      <c r="D80" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="E80" s="22"/>
-      <c r="F80" s="22"/>
+      <c r="E80" s="27"/>
+      <c r="F80" s="27"/>
       <c r="G80" s="8" t="s">
         <v>12</v>
       </c>
@@ -16968,17 +16964,17 @@
         <v>6.6343181818181822</v>
       </c>
     </row>
-    <row r="81" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A81" s="21" t="s">
+    <row r="81" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A81" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="B81" s="21"/>
-      <c r="C81" s="21"/>
-      <c r="D81" s="22" t="s">
+      <c r="B81" s="26"/>
+      <c r="C81" s="26"/>
+      <c r="D81" s="27" t="s">
         <v>157</v>
       </c>
-      <c r="E81" s="22"/>
-      <c r="F81" s="22"/>
+      <c r="E81" s="27"/>
+      <c r="F81" s="27"/>
       <c r="G81" s="8" t="s">
         <v>12</v>
       </c>
@@ -17015,17 +17011,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A82" s="21" t="s">
+    <row r="82" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A82" s="26" t="s">
         <v>158</v>
       </c>
-      <c r="B82" s="21"/>
-      <c r="C82" s="21"/>
-      <c r="D82" s="22" t="s">
+      <c r="B82" s="26"/>
+      <c r="C82" s="26"/>
+      <c r="D82" s="27" t="s">
         <v>159</v>
       </c>
-      <c r="E82" s="22"/>
-      <c r="F82" s="22"/>
+      <c r="E82" s="27"/>
+      <c r="F82" s="27"/>
       <c r="G82" s="8" t="s">
         <v>12</v>
       </c>
@@ -17062,17 +17058,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A83" s="21" t="s">
+    <row r="83" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A83" s="26" t="s">
         <v>160</v>
       </c>
-      <c r="B83" s="21"/>
-      <c r="C83" s="21"/>
-      <c r="D83" s="22" t="s">
+      <c r="B83" s="26"/>
+      <c r="C83" s="26"/>
+      <c r="D83" s="27" t="s">
         <v>161</v>
       </c>
-      <c r="E83" s="22"/>
-      <c r="F83" s="22"/>
+      <c r="E83" s="27"/>
+      <c r="F83" s="27"/>
       <c r="G83" s="8" t="s">
         <v>12</v>
       </c>
@@ -17109,17 +17105,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A84" s="21" t="s">
+    <row r="84" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A84" s="26" t="s">
         <v>162</v>
       </c>
-      <c r="B84" s="21"/>
-      <c r="C84" s="21"/>
-      <c r="D84" s="22" t="s">
+      <c r="B84" s="26"/>
+      <c r="C84" s="26"/>
+      <c r="D84" s="27" t="s">
         <v>163</v>
       </c>
-      <c r="E84" s="22"/>
-      <c r="F84" s="22"/>
+      <c r="E84" s="27"/>
+      <c r="F84" s="27"/>
       <c r="G84" s="8" t="s">
         <v>12</v>
       </c>
@@ -17156,17 +17152,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A85" s="21" t="s">
+    <row r="85" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A85" s="26" t="s">
         <v>164</v>
       </c>
-      <c r="B85" s="21"/>
-      <c r="C85" s="21"/>
-      <c r="D85" s="22" t="s">
+      <c r="B85" s="26"/>
+      <c r="C85" s="26"/>
+      <c r="D85" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="E85" s="22"/>
-      <c r="F85" s="22"/>
+      <c r="E85" s="27"/>
+      <c r="F85" s="27"/>
       <c r="G85" s="8" t="s">
         <v>12</v>
       </c>
@@ -17205,17 +17201,17 @@
         <v>10.079772727272726</v>
       </c>
     </row>
-    <row r="86" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A86" s="21" t="s">
+    <row r="86" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A86" s="26" t="s">
         <v>166</v>
       </c>
-      <c r="B86" s="21"/>
-      <c r="C86" s="21"/>
-      <c r="D86" s="22" t="s">
+      <c r="B86" s="26"/>
+      <c r="C86" s="26"/>
+      <c r="D86" s="27" t="s">
         <v>167</v>
       </c>
-      <c r="E86" s="22"/>
-      <c r="F86" s="22"/>
+      <c r="E86" s="27"/>
+      <c r="F86" s="27"/>
       <c r="G86" s="8" t="s">
         <v>12</v>
       </c>
@@ -17254,17 +17250,17 @@
         <v>3.806</v>
       </c>
     </row>
-    <row r="87" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A87" s="21" t="s">
+    <row r="87" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A87" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="B87" s="21"/>
-      <c r="C87" s="21"/>
-      <c r="D87" s="22" t="s">
+      <c r="B87" s="26"/>
+      <c r="C87" s="26"/>
+      <c r="D87" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="E87" s="22"/>
-      <c r="F87" s="22"/>
+      <c r="E87" s="27"/>
+      <c r="F87" s="27"/>
       <c r="G87" s="8" t="s">
         <v>12</v>
       </c>
@@ -17303,17 +17299,17 @@
         <v>5.7990000000000004</v>
       </c>
     </row>
-    <row r="88" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A88" s="21" t="s">
+    <row r="88" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A88" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="B88" s="21"/>
-      <c r="C88" s="21"/>
-      <c r="D88" s="22" t="s">
+      <c r="B88" s="26"/>
+      <c r="C88" s="26"/>
+      <c r="D88" s="27" t="s">
         <v>171</v>
       </c>
-      <c r="E88" s="22"/>
-      <c r="F88" s="22"/>
+      <c r="E88" s="27"/>
+      <c r="F88" s="27"/>
       <c r="G88" s="8" t="s">
         <v>12</v>
       </c>
@@ -17352,17 +17348,17 @@
         <v>92.123000000000005</v>
       </c>
     </row>
-    <row r="89" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A89" s="21" t="s">
+    <row r="89" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A89" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="B89" s="21"/>
-      <c r="C89" s="21"/>
-      <c r="D89" s="22" t="s">
+      <c r="B89" s="26"/>
+      <c r="C89" s="26"/>
+      <c r="D89" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="E89" s="22"/>
-      <c r="F89" s="22"/>
+      <c r="E89" s="27"/>
+      <c r="F89" s="27"/>
       <c r="G89" s="8" t="s">
         <v>12</v>
       </c>
@@ -17401,17 +17397,17 @@
         <v>76.117000000000004</v>
       </c>
     </row>
-    <row r="90" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A90" s="21" t="s">
+    <row r="90" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A90" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="B90" s="21"/>
-      <c r="C90" s="21"/>
-      <c r="D90" s="22" t="s">
+      <c r="B90" s="26"/>
+      <c r="C90" s="26"/>
+      <c r="D90" s="27" t="s">
         <v>175</v>
       </c>
-      <c r="E90" s="22"/>
-      <c r="F90" s="22"/>
+      <c r="E90" s="27"/>
+      <c r="F90" s="27"/>
       <c r="G90" s="8" t="s">
         <v>12</v>
       </c>
@@ -17450,67 +17446,64 @@
         <v>283.62863636363636</v>
       </c>
     </row>
-    <row r="91" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A91" s="21" t="s">
+    <row r="91" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A91" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="B91" s="21"/>
-      <c r="C91" s="21"/>
-      <c r="D91" s="27" t="s">
+      <c r="B91" s="26"/>
+      <c r="C91" s="26"/>
+      <c r="D91" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="E91" s="27"/>
-      <c r="F91" s="27"/>
-      <c r="G91" s="28" t="s">
+      <c r="E91" s="30"/>
+      <c r="F91" s="30"/>
+      <c r="G91" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H91" s="29">
+      <c r="H91" s="19">
         <v>1273.989</v>
       </c>
-      <c r="I91" s="29">
+      <c r="I91" s="19">
         <v>1273.989</v>
       </c>
-      <c r="J91" s="30">
+      <c r="J91" s="20">
         <f>IF(IFERROR(VLOOKUP(D91,[1]TDSheet!$A:$N,14,0),0)&gt;1,1,IFERROR(VLOOKUP(D91,[1]TDSheet!$A:$N,14,0),0))</f>
         <v>0.33773273844595425</v>
       </c>
-      <c r="K91" s="31">
+      <c r="K91" s="21">
         <f>IFERROR(VLOOKUP(D91,[1]TDSheet!$A:$M,12,0),0)</f>
         <v>96.506454545454531</v>
       </c>
-      <c r="L91" s="31">
+      <c r="L91" s="21">
         <f>IFERROR(VLOOKUP(D91,[1]TDSheet!$A:$M,13,0),0)</f>
         <v>96.506454545454531</v>
       </c>
-      <c r="M91" s="31">
+      <c r="M91" s="21">
         <f t="shared" si="9"/>
         <v>482.53227272727264</v>
       </c>
-      <c r="N91" s="31">
+      <c r="N91" s="21">
         <f t="shared" si="10"/>
         <v>482.53227272727264</v>
       </c>
-      <c r="O91" s="32">
+      <c r="O91" s="22">
         <v>0</v>
       </c>
-      <c r="P91" s="32">
+      <c r="P91" s="22">
         <v>0</v>
       </c>
-      <c r="Q91" t="s">
-        <v>400</v>
-      </c>
     </row>
-    <row r="92" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A92" s="21" t="s">
+    <row r="92" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A92" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="B92" s="21"/>
-      <c r="C92" s="21"/>
-      <c r="D92" s="22" t="s">
+      <c r="B92" s="26"/>
+      <c r="C92" s="26"/>
+      <c r="D92" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="E92" s="22"/>
-      <c r="F92" s="22"/>
+      <c r="E92" s="27"/>
+      <c r="F92" s="27"/>
       <c r="G92" s="8" t="s">
         <v>12</v>
       </c>
@@ -17549,17 +17542,17 @@
         <v>5.4189999999999996</v>
       </c>
     </row>
-    <row r="93" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A93" s="21" t="s">
+    <row r="93" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A93" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="B93" s="21"/>
-      <c r="C93" s="21"/>
-      <c r="D93" s="22" t="s">
+      <c r="B93" s="26"/>
+      <c r="C93" s="26"/>
+      <c r="D93" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="E93" s="22"/>
-      <c r="F93" s="22"/>
+      <c r="E93" s="27"/>
+      <c r="F93" s="27"/>
       <c r="G93" s="8" t="s">
         <v>12</v>
       </c>
@@ -17596,17 +17589,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A94" s="21" t="s">
+    <row r="94" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A94" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="B94" s="21"/>
-      <c r="C94" s="21"/>
-      <c r="D94" s="22" t="s">
+      <c r="B94" s="26"/>
+      <c r="C94" s="26"/>
+      <c r="D94" s="27" t="s">
         <v>183</v>
       </c>
-      <c r="E94" s="22"/>
-      <c r="F94" s="22"/>
+      <c r="E94" s="27"/>
+      <c r="F94" s="27"/>
       <c r="G94" s="8" t="s">
         <v>12</v>
       </c>
@@ -17643,17 +17636,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A95" s="21" t="s">
+    <row r="95" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A95" s="26" t="s">
         <v>184</v>
       </c>
-      <c r="B95" s="21"/>
-      <c r="C95" s="21"/>
-      <c r="D95" s="22" t="s">
+      <c r="B95" s="26"/>
+      <c r="C95" s="26"/>
+      <c r="D95" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="E95" s="22"/>
-      <c r="F95" s="22"/>
+      <c r="E95" s="27"/>
+      <c r="F95" s="27"/>
       <c r="G95" s="8" t="s">
         <v>12</v>
       </c>
@@ -17692,17 +17685,17 @@
         <v>21.648181818181818</v>
       </c>
     </row>
-    <row r="96" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A96" s="21" t="s">
+    <row r="96" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A96" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="B96" s="21"/>
-      <c r="C96" s="21"/>
-      <c r="D96" s="22" t="s">
+      <c r="B96" s="26"/>
+      <c r="C96" s="26"/>
+      <c r="D96" s="27" t="s">
         <v>187</v>
       </c>
-      <c r="E96" s="22"/>
-      <c r="F96" s="22"/>
+      <c r="E96" s="27"/>
+      <c r="F96" s="27"/>
       <c r="G96" s="8" t="s">
         <v>12</v>
       </c>
@@ -17741,17 +17734,17 @@
         <v>26.719000000000001</v>
       </c>
     </row>
-    <row r="97" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A97" s="21" t="s">
+    <row r="97" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A97" s="26" t="s">
         <v>188</v>
       </c>
-      <c r="B97" s="21"/>
-      <c r="C97" s="21"/>
-      <c r="D97" s="22" t="s">
+      <c r="B97" s="26"/>
+      <c r="C97" s="26"/>
+      <c r="D97" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="E97" s="22"/>
-      <c r="F97" s="22"/>
+      <c r="E97" s="27"/>
+      <c r="F97" s="27"/>
       <c r="G97" s="8" t="s">
         <v>12</v>
       </c>
@@ -17790,83 +17783,80 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="98" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A98" s="21" t="s">
+    <row r="98" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A98" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="B98" s="21"/>
-      <c r="C98" s="21"/>
-      <c r="D98" s="27" t="s">
+      <c r="B98" s="26"/>
+      <c r="C98" s="26"/>
+      <c r="D98" s="30" t="s">
         <v>191</v>
       </c>
-      <c r="E98" s="27"/>
-      <c r="F98" s="27"/>
-      <c r="G98" s="28" t="s">
+      <c r="E98" s="30"/>
+      <c r="F98" s="30"/>
+      <c r="G98" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H98" s="33">
+      <c r="H98" s="23">
         <v>548.10599999999999</v>
       </c>
-      <c r="I98" s="33">
+      <c r="I98" s="23">
         <v>548.10599999999999</v>
       </c>
-      <c r="J98" s="30">
+      <c r="J98" s="20">
         <f>IF(IFERROR(VLOOKUP(D98,[1]TDSheet!$A:$N,14,0),0)&gt;1,1,IFERROR(VLOOKUP(D98,[1]TDSheet!$A:$N,14,0),0))</f>
         <v>0.31664985578029059</v>
       </c>
-      <c r="K98" s="31">
+      <c r="K98" s="21">
         <f>IFERROR(VLOOKUP(D98,[1]TDSheet!$A:$M,12,0),0)</f>
         <v>36.601772727272731</v>
       </c>
-      <c r="L98" s="31">
+      <c r="L98" s="21">
         <f>IFERROR(VLOOKUP(D98,[1]TDSheet!$A:$M,13,0),0)</f>
         <v>36.601772727272731</v>
       </c>
-      <c r="M98" s="31">
+      <c r="M98" s="21">
         <f t="shared" si="9"/>
         <v>183.00886363636366</v>
       </c>
-      <c r="N98" s="31">
+      <c r="N98" s="21">
         <f t="shared" si="10"/>
         <v>183.00886363636366</v>
       </c>
-      <c r="O98" s="32">
+      <c r="O98" s="22">
         <v>0</v>
       </c>
-      <c r="P98" s="32">
+      <c r="P98" s="22">
         <v>0</v>
       </c>
-      <c r="Q98" t="s">
-        <v>400</v>
-      </c>
     </row>
-    <row r="99" spans="1:17" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="23" t="s">
+    <row r="99" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="B99" s="23"/>
-      <c r="C99" s="23"/>
-      <c r="D99" s="24" t="s">
+      <c r="B99" s="24"/>
+      <c r="C99" s="24"/>
+      <c r="D99" s="25" t="s">
         <v>193</v>
       </c>
-      <c r="E99" s="24"/>
-      <c r="F99" s="24"/>
+      <c r="E99" s="25"/>
+      <c r="F99" s="25"/>
       <c r="G99" s="5"/>
       <c r="H99" s="7"/>
       <c r="I99" s="7"/>
       <c r="J99" s="12"/>
     </row>
-    <row r="100" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A100" s="21" t="s">
+    <row r="100" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A100" s="26" t="s">
         <v>194</v>
       </c>
-      <c r="B100" s="21"/>
-      <c r="C100" s="21"/>
-      <c r="D100" s="22" t="s">
+      <c r="B100" s="26"/>
+      <c r="C100" s="26"/>
+      <c r="D100" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="E100" s="22"/>
-      <c r="F100" s="22"/>
+      <c r="E100" s="27"/>
+      <c r="F100" s="27"/>
       <c r="G100" s="8" t="s">
         <v>13</v>
       </c>
@@ -17905,17 +17895,17 @@
         <v>19.55</v>
       </c>
     </row>
-    <row r="101" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A101" s="21" t="s">
+    <row r="101" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A101" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="B101" s="21"/>
-      <c r="C101" s="21"/>
-      <c r="D101" s="22" t="s">
+      <c r="B101" s="26"/>
+      <c r="C101" s="26"/>
+      <c r="D101" s="27" t="s">
         <v>197</v>
       </c>
-      <c r="E101" s="22"/>
-      <c r="F101" s="22"/>
+      <c r="E101" s="27"/>
+      <c r="F101" s="27"/>
       <c r="G101" s="8" t="s">
         <v>13</v>
       </c>
@@ -17954,17 +17944,17 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="102" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A102" s="21" t="s">
+    <row r="102" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A102" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="B102" s="21"/>
-      <c r="C102" s="21"/>
-      <c r="D102" s="22" t="s">
+      <c r="B102" s="26"/>
+      <c r="C102" s="26"/>
+      <c r="D102" s="27" t="s">
         <v>199</v>
       </c>
-      <c r="E102" s="22"/>
-      <c r="F102" s="22"/>
+      <c r="E102" s="27"/>
+      <c r="F102" s="27"/>
       <c r="G102" s="8" t="s">
         <v>13</v>
       </c>
@@ -18003,17 +17993,17 @@
         <v>58.14</v>
       </c>
     </row>
-    <row r="103" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A103" s="21" t="s">
+    <row r="103" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A103" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="B103" s="21"/>
-      <c r="C103" s="21"/>
-      <c r="D103" s="22" t="s">
+      <c r="B103" s="26"/>
+      <c r="C103" s="26"/>
+      <c r="D103" s="27" t="s">
         <v>201</v>
       </c>
-      <c r="E103" s="22"/>
-      <c r="F103" s="22"/>
+      <c r="E103" s="27"/>
+      <c r="F103" s="27"/>
       <c r="G103" s="8" t="s">
         <v>13</v>
       </c>
@@ -18052,17 +18042,17 @@
         <v>177.00200000000001</v>
       </c>
     </row>
-    <row r="104" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A104" s="21" t="s">
+    <row r="104" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A104" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="B104" s="21"/>
-      <c r="C104" s="21"/>
-      <c r="D104" s="22" t="s">
+      <c r="B104" s="26"/>
+      <c r="C104" s="26"/>
+      <c r="D104" s="27" t="s">
         <v>203</v>
       </c>
-      <c r="E104" s="22"/>
-      <c r="F104" s="22"/>
+      <c r="E104" s="27"/>
+      <c r="F104" s="27"/>
       <c r="G104" s="8" t="s">
         <v>13</v>
       </c>
@@ -18099,17 +18089,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A105" s="21" t="s">
+    <row r="105" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A105" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="B105" s="21"/>
-      <c r="C105" s="21"/>
-      <c r="D105" s="22" t="s">
+      <c r="B105" s="26"/>
+      <c r="C105" s="26"/>
+      <c r="D105" s="27" t="s">
         <v>205</v>
       </c>
-      <c r="E105" s="22"/>
-      <c r="F105" s="22"/>
+      <c r="E105" s="27"/>
+      <c r="F105" s="27"/>
       <c r="G105" s="8" t="s">
         <v>13</v>
       </c>
@@ -18148,17 +18138,17 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="106" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A106" s="21" t="s">
+    <row r="106" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A106" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="B106" s="21"/>
-      <c r="C106" s="21"/>
-      <c r="D106" s="22" t="s">
+      <c r="B106" s="26"/>
+      <c r="C106" s="26"/>
+      <c r="D106" s="27" t="s">
         <v>207</v>
       </c>
-      <c r="E106" s="22"/>
-      <c r="F106" s="22"/>
+      <c r="E106" s="27"/>
+      <c r="F106" s="27"/>
       <c r="G106" s="8" t="s">
         <v>13</v>
       </c>
@@ -18197,17 +18187,17 @@
         <v>25</v>
       </c>
     </row>
-    <row r="107" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A107" s="21" t="s">
+    <row r="107" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A107" s="26" t="s">
         <v>208</v>
       </c>
-      <c r="B107" s="21"/>
-      <c r="C107" s="21"/>
-      <c r="D107" s="22" t="s">
+      <c r="B107" s="26"/>
+      <c r="C107" s="26"/>
+      <c r="D107" s="27" t="s">
         <v>209</v>
       </c>
-      <c r="E107" s="22"/>
-      <c r="F107" s="22"/>
+      <c r="E107" s="27"/>
+      <c r="F107" s="27"/>
       <c r="G107" s="8" t="s">
         <v>13</v>
       </c>
@@ -18244,17 +18234,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A108" s="21" t="s">
+    <row r="108" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A108" s="26" t="s">
         <v>210</v>
       </c>
-      <c r="B108" s="21"/>
-      <c r="C108" s="21"/>
-      <c r="D108" s="22" t="s">
+      <c r="B108" s="26"/>
+      <c r="C108" s="26"/>
+      <c r="D108" s="27" t="s">
         <v>211</v>
       </c>
-      <c r="E108" s="22"/>
-      <c r="F108" s="22"/>
+      <c r="E108" s="27"/>
+      <c r="F108" s="27"/>
       <c r="G108" s="8" t="s">
         <v>13</v>
       </c>
@@ -18293,17 +18283,17 @@
         <v>20</v>
       </c>
     </row>
-    <row r="109" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A109" s="21" t="s">
+    <row r="109" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A109" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="B109" s="21"/>
-      <c r="C109" s="21"/>
-      <c r="D109" s="22" t="s">
+      <c r="B109" s="26"/>
+      <c r="C109" s="26"/>
+      <c r="D109" s="27" t="s">
         <v>213</v>
       </c>
-      <c r="E109" s="22"/>
-      <c r="F109" s="22"/>
+      <c r="E109" s="27"/>
+      <c r="F109" s="27"/>
       <c r="G109" s="8" t="s">
         <v>13</v>
       </c>
@@ -18342,17 +18332,17 @@
         <v>42</v>
       </c>
     </row>
-    <row r="110" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A110" s="21" t="s">
+    <row r="110" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A110" s="26" t="s">
         <v>214</v>
       </c>
-      <c r="B110" s="21"/>
-      <c r="C110" s="21"/>
-      <c r="D110" s="22" t="s">
+      <c r="B110" s="26"/>
+      <c r="C110" s="26"/>
+      <c r="D110" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="E110" s="22"/>
-      <c r="F110" s="22"/>
+      <c r="E110" s="27"/>
+      <c r="F110" s="27"/>
       <c r="G110" s="8" t="s">
         <v>13</v>
       </c>
@@ -18389,17 +18379,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A111" s="21" t="s">
+    <row r="111" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A111" s="26" t="s">
         <v>216</v>
       </c>
-      <c r="B111" s="21"/>
-      <c r="C111" s="21"/>
-      <c r="D111" s="22" t="s">
+      <c r="B111" s="26"/>
+      <c r="C111" s="26"/>
+      <c r="D111" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E111" s="22"/>
-      <c r="F111" s="22"/>
+      <c r="E111" s="27"/>
+      <c r="F111" s="27"/>
       <c r="G111" s="8" t="s">
         <v>13</v>
       </c>
@@ -18438,17 +18428,17 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="112" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A112" s="21" t="s">
+    <row r="112" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A112" s="26" t="s">
         <v>218</v>
       </c>
-      <c r="B112" s="21"/>
-      <c r="C112" s="21"/>
-      <c r="D112" s="22" t="s">
+      <c r="B112" s="26"/>
+      <c r="C112" s="26"/>
+      <c r="D112" s="27" t="s">
         <v>219</v>
       </c>
-      <c r="E112" s="22"/>
-      <c r="F112" s="22"/>
+      <c r="E112" s="27"/>
+      <c r="F112" s="27"/>
       <c r="G112" s="8" t="s">
         <v>13</v>
       </c>
@@ -18486,16 +18476,16 @@
       </c>
     </row>
     <row r="113" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A113" s="21" t="s">
+      <c r="A113" s="26" t="s">
         <v>220</v>
       </c>
-      <c r="B113" s="21"/>
-      <c r="C113" s="21"/>
-      <c r="D113" s="22" t="s">
+      <c r="B113" s="26"/>
+      <c r="C113" s="26"/>
+      <c r="D113" s="27" t="s">
         <v>221</v>
       </c>
-      <c r="E113" s="22"/>
-      <c r="F113" s="22"/>
+      <c r="E113" s="27"/>
+      <c r="F113" s="27"/>
       <c r="G113" s="8" t="s">
         <v>13</v>
       </c>
@@ -18533,16 +18523,16 @@
       </c>
     </row>
     <row r="114" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A114" s="21" t="s">
+      <c r="A114" s="26" t="s">
         <v>222</v>
       </c>
-      <c r="B114" s="21"/>
-      <c r="C114" s="21"/>
-      <c r="D114" s="22" t="s">
+      <c r="B114" s="26"/>
+      <c r="C114" s="26"/>
+      <c r="D114" s="27" t="s">
         <v>223</v>
       </c>
-      <c r="E114" s="22"/>
-      <c r="F114" s="22"/>
+      <c r="E114" s="27"/>
+      <c r="F114" s="27"/>
       <c r="G114" s="8" t="s">
         <v>13</v>
       </c>
@@ -18582,16 +18572,16 @@
       </c>
     </row>
     <row r="115" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A115" s="21" t="s">
+      <c r="A115" s="26" t="s">
         <v>224</v>
       </c>
-      <c r="B115" s="21"/>
-      <c r="C115" s="21"/>
-      <c r="D115" s="22" t="s">
+      <c r="B115" s="26"/>
+      <c r="C115" s="26"/>
+      <c r="D115" s="27" t="s">
         <v>225</v>
       </c>
-      <c r="E115" s="22"/>
-      <c r="F115" s="22"/>
+      <c r="E115" s="27"/>
+      <c r="F115" s="27"/>
       <c r="G115" s="8" t="s">
         <v>13</v>
       </c>
@@ -18629,16 +18619,16 @@
       </c>
     </row>
     <row r="116" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A116" s="21" t="s">
+      <c r="A116" s="26" t="s">
         <v>226</v>
       </c>
-      <c r="B116" s="21"/>
-      <c r="C116" s="21"/>
-      <c r="D116" s="22" t="s">
+      <c r="B116" s="26"/>
+      <c r="C116" s="26"/>
+      <c r="D116" s="27" t="s">
         <v>227</v>
       </c>
-      <c r="E116" s="22"/>
-      <c r="F116" s="22"/>
+      <c r="E116" s="27"/>
+      <c r="F116" s="27"/>
       <c r="G116" s="8" t="s">
         <v>13</v>
       </c>
@@ -18678,16 +18668,16 @@
       </c>
     </row>
     <row r="117" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A117" s="21" t="s">
+      <c r="A117" s="26" t="s">
         <v>228</v>
       </c>
-      <c r="B117" s="21"/>
-      <c r="C117" s="21"/>
-      <c r="D117" s="22" t="s">
+      <c r="B117" s="26"/>
+      <c r="C117" s="26"/>
+      <c r="D117" s="27" t="s">
         <v>229</v>
       </c>
-      <c r="E117" s="22"/>
-      <c r="F117" s="22"/>
+      <c r="E117" s="27"/>
+      <c r="F117" s="27"/>
       <c r="G117" s="8" t="s">
         <v>13</v>
       </c>
@@ -18727,16 +18717,16 @@
       </c>
     </row>
     <row r="118" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A118" s="21" t="s">
+      <c r="A118" s="26" t="s">
         <v>230</v>
       </c>
-      <c r="B118" s="21"/>
-      <c r="C118" s="21"/>
-      <c r="D118" s="22" t="s">
+      <c r="B118" s="26"/>
+      <c r="C118" s="26"/>
+      <c r="D118" s="27" t="s">
         <v>231</v>
       </c>
-      <c r="E118" s="22"/>
-      <c r="F118" s="22"/>
+      <c r="E118" s="27"/>
+      <c r="F118" s="27"/>
       <c r="G118" s="8" t="s">
         <v>13</v>
       </c>
@@ -18776,16 +18766,16 @@
       </c>
     </row>
     <row r="119" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A119" s="21" t="s">
+      <c r="A119" s="26" t="s">
         <v>232</v>
       </c>
-      <c r="B119" s="21"/>
-      <c r="C119" s="21"/>
-      <c r="D119" s="22" t="s">
+      <c r="B119" s="26"/>
+      <c r="C119" s="26"/>
+      <c r="D119" s="27" t="s">
         <v>233</v>
       </c>
-      <c r="E119" s="22"/>
-      <c r="F119" s="22"/>
+      <c r="E119" s="27"/>
+      <c r="F119" s="27"/>
       <c r="G119" s="8" t="s">
         <v>13</v>
       </c>
@@ -18825,16 +18815,16 @@
       </c>
     </row>
     <row r="120" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A120" s="21" t="s">
+      <c r="A120" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="B120" s="21"/>
-      <c r="C120" s="21"/>
-      <c r="D120" s="22" t="s">
+      <c r="B120" s="26"/>
+      <c r="C120" s="26"/>
+      <c r="D120" s="27" t="s">
         <v>235</v>
       </c>
-      <c r="E120" s="22"/>
-      <c r="F120" s="22"/>
+      <c r="E120" s="27"/>
+      <c r="F120" s="27"/>
       <c r="G120" s="8" t="s">
         <v>13</v>
       </c>
@@ -18872,16 +18862,16 @@
       </c>
     </row>
     <row r="121" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A121" s="21" t="s">
+      <c r="A121" s="26" t="s">
         <v>236</v>
       </c>
-      <c r="B121" s="21"/>
-      <c r="C121" s="21"/>
-      <c r="D121" s="22" t="s">
+      <c r="B121" s="26"/>
+      <c r="C121" s="26"/>
+      <c r="D121" s="27" t="s">
         <v>237</v>
       </c>
-      <c r="E121" s="22"/>
-      <c r="F121" s="22"/>
+      <c r="E121" s="27"/>
+      <c r="F121" s="27"/>
       <c r="G121" s="8" t="s">
         <v>13</v>
       </c>
@@ -18921,16 +18911,16 @@
       </c>
     </row>
     <row r="122" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A122" s="21" t="s">
+      <c r="A122" s="26" t="s">
         <v>238</v>
       </c>
-      <c r="B122" s="21"/>
-      <c r="C122" s="21"/>
-      <c r="D122" s="22" t="s">
+      <c r="B122" s="26"/>
+      <c r="C122" s="26"/>
+      <c r="D122" s="27" t="s">
         <v>239</v>
       </c>
-      <c r="E122" s="22"/>
-      <c r="F122" s="22"/>
+      <c r="E122" s="27"/>
+      <c r="F122" s="27"/>
       <c r="G122" s="8" t="s">
         <v>13</v>
       </c>
@@ -18970,16 +18960,16 @@
       </c>
     </row>
     <row r="123" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A123" s="21" t="s">
+      <c r="A123" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="B123" s="21"/>
-      <c r="C123" s="21"/>
-      <c r="D123" s="22" t="s">
+      <c r="B123" s="26"/>
+      <c r="C123" s="26"/>
+      <c r="D123" s="27" t="s">
         <v>241</v>
       </c>
-      <c r="E123" s="22"/>
-      <c r="F123" s="22"/>
+      <c r="E123" s="27"/>
+      <c r="F123" s="27"/>
       <c r="G123" s="8" t="s">
         <v>13</v>
       </c>
@@ -19017,16 +19007,16 @@
       </c>
     </row>
     <row r="124" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A124" s="21" t="s">
+      <c r="A124" s="26" t="s">
         <v>242</v>
       </c>
-      <c r="B124" s="21"/>
-      <c r="C124" s="21"/>
-      <c r="D124" s="22" t="s">
+      <c r="B124" s="26"/>
+      <c r="C124" s="26"/>
+      <c r="D124" s="27" t="s">
         <v>243</v>
       </c>
-      <c r="E124" s="22"/>
-      <c r="F124" s="22"/>
+      <c r="E124" s="27"/>
+      <c r="F124" s="27"/>
       <c r="G124" s="8" t="s">
         <v>13</v>
       </c>
@@ -19066,16 +19056,16 @@
       </c>
     </row>
     <row r="125" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A125" s="21" t="s">
+      <c r="A125" s="26" t="s">
         <v>244</v>
       </c>
-      <c r="B125" s="21"/>
-      <c r="C125" s="21"/>
-      <c r="D125" s="22" t="s">
+      <c r="B125" s="26"/>
+      <c r="C125" s="26"/>
+      <c r="D125" s="27" t="s">
         <v>245</v>
       </c>
-      <c r="E125" s="22"/>
-      <c r="F125" s="22"/>
+      <c r="E125" s="27"/>
+      <c r="F125" s="27"/>
       <c r="G125" s="8" t="s">
         <v>13</v>
       </c>
@@ -19113,16 +19103,16 @@
       </c>
     </row>
     <row r="126" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A126" s="21" t="s">
+      <c r="A126" s="26" t="s">
         <v>246</v>
       </c>
-      <c r="B126" s="21"/>
-      <c r="C126" s="21"/>
-      <c r="D126" s="22" t="s">
+      <c r="B126" s="26"/>
+      <c r="C126" s="26"/>
+      <c r="D126" s="27" t="s">
         <v>247</v>
       </c>
-      <c r="E126" s="22"/>
-      <c r="F126" s="22"/>
+      <c r="E126" s="27"/>
+      <c r="F126" s="27"/>
       <c r="G126" s="8" t="s">
         <v>13</v>
       </c>
@@ -19162,16 +19152,16 @@
       </c>
     </row>
     <row r="127" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A127" s="21" t="s">
+      <c r="A127" s="26" t="s">
         <v>248</v>
       </c>
-      <c r="B127" s="21"/>
-      <c r="C127" s="21"/>
-      <c r="D127" s="22" t="s">
+      <c r="B127" s="26"/>
+      <c r="C127" s="26"/>
+      <c r="D127" s="27" t="s">
         <v>249</v>
       </c>
-      <c r="E127" s="22"/>
-      <c r="F127" s="22"/>
+      <c r="E127" s="27"/>
+      <c r="F127" s="27"/>
       <c r="G127" s="8" t="s">
         <v>13</v>
       </c>
@@ -19211,16 +19201,16 @@
       </c>
     </row>
     <row r="128" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A128" s="21" t="s">
+      <c r="A128" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="B128" s="21"/>
-      <c r="C128" s="21"/>
-      <c r="D128" s="22" t="s">
+      <c r="B128" s="26"/>
+      <c r="C128" s="26"/>
+      <c r="D128" s="27" t="s">
         <v>251</v>
       </c>
-      <c r="E128" s="22"/>
-      <c r="F128" s="22"/>
+      <c r="E128" s="27"/>
+      <c r="F128" s="27"/>
       <c r="G128" s="8" t="s">
         <v>13</v>
       </c>
@@ -19260,16 +19250,16 @@
       </c>
     </row>
     <row r="129" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A129" s="21" t="s">
+      <c r="A129" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="B129" s="21"/>
-      <c r="C129" s="21"/>
-      <c r="D129" s="22" t="s">
+      <c r="B129" s="26"/>
+      <c r="C129" s="26"/>
+      <c r="D129" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="E129" s="22"/>
-      <c r="F129" s="22"/>
+      <c r="E129" s="27"/>
+      <c r="F129" s="27"/>
       <c r="G129" s="8" t="s">
         <v>13</v>
       </c>
@@ -19309,16 +19299,16 @@
       </c>
     </row>
     <row r="130" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A130" s="21" t="s">
+      <c r="A130" s="26" t="s">
         <v>254</v>
       </c>
-      <c r="B130" s="21"/>
-      <c r="C130" s="21"/>
-      <c r="D130" s="22" t="s">
+      <c r="B130" s="26"/>
+      <c r="C130" s="26"/>
+      <c r="D130" s="27" t="s">
         <v>255</v>
       </c>
-      <c r="E130" s="22"/>
-      <c r="F130" s="22"/>
+      <c r="E130" s="27"/>
+      <c r="F130" s="27"/>
       <c r="G130" s="8" t="s">
         <v>13</v>
       </c>
@@ -19356,16 +19346,16 @@
       </c>
     </row>
     <row r="131" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A131" s="21" t="s">
+      <c r="A131" s="26" t="s">
         <v>256</v>
       </c>
-      <c r="B131" s="21"/>
-      <c r="C131" s="21"/>
-      <c r="D131" s="22" t="s">
+      <c r="B131" s="26"/>
+      <c r="C131" s="26"/>
+      <c r="D131" s="27" t="s">
         <v>257</v>
       </c>
-      <c r="E131" s="22"/>
-      <c r="F131" s="22"/>
+      <c r="E131" s="27"/>
+      <c r="F131" s="27"/>
       <c r="G131" s="8" t="s">
         <v>13</v>
       </c>
@@ -19405,16 +19395,16 @@
       </c>
     </row>
     <row r="132" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A132" s="21" t="s">
+      <c r="A132" s="26" t="s">
         <v>258</v>
       </c>
-      <c r="B132" s="21"/>
-      <c r="C132" s="21"/>
-      <c r="D132" s="22" t="s">
+      <c r="B132" s="26"/>
+      <c r="C132" s="26"/>
+      <c r="D132" s="27" t="s">
         <v>259</v>
       </c>
-      <c r="E132" s="22"/>
-      <c r="F132" s="22"/>
+      <c r="E132" s="27"/>
+      <c r="F132" s="27"/>
       <c r="G132" s="8" t="s">
         <v>13</v>
       </c>
@@ -19454,16 +19444,16 @@
       </c>
     </row>
     <row r="133" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A133" s="21" t="s">
+      <c r="A133" s="26" t="s">
         <v>260</v>
       </c>
-      <c r="B133" s="21"/>
-      <c r="C133" s="21"/>
-      <c r="D133" s="22" t="s">
+      <c r="B133" s="26"/>
+      <c r="C133" s="26"/>
+      <c r="D133" s="27" t="s">
         <v>261</v>
       </c>
-      <c r="E133" s="22"/>
-      <c r="F133" s="22"/>
+      <c r="E133" s="27"/>
+      <c r="F133" s="27"/>
       <c r="G133" s="8" t="s">
         <v>13</v>
       </c>
@@ -19501,16 +19491,16 @@
       </c>
     </row>
     <row r="134" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A134" s="21" t="s">
+      <c r="A134" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="B134" s="21"/>
-      <c r="C134" s="21"/>
-      <c r="D134" s="22" t="s">
+      <c r="B134" s="26"/>
+      <c r="C134" s="26"/>
+      <c r="D134" s="27" t="s">
         <v>263</v>
       </c>
-      <c r="E134" s="22"/>
-      <c r="F134" s="22"/>
+      <c r="E134" s="27"/>
+      <c r="F134" s="27"/>
       <c r="G134" s="8" t="s">
         <v>13</v>
       </c>
@@ -19548,16 +19538,16 @@
       </c>
     </row>
     <row r="135" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A135" s="21" t="s">
+      <c r="A135" s="26" t="s">
         <v>264</v>
       </c>
-      <c r="B135" s="21"/>
-      <c r="C135" s="21"/>
-      <c r="D135" s="22" t="s">
+      <c r="B135" s="26"/>
+      <c r="C135" s="26"/>
+      <c r="D135" s="27" t="s">
         <v>265</v>
       </c>
-      <c r="E135" s="22"/>
-      <c r="F135" s="22"/>
+      <c r="E135" s="27"/>
+      <c r="F135" s="27"/>
       <c r="G135" s="8" t="s">
         <v>13</v>
       </c>
@@ -19595,16 +19585,16 @@
       </c>
     </row>
     <row r="136" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A136" s="21" t="s">
+      <c r="A136" s="26" t="s">
         <v>266</v>
       </c>
-      <c r="B136" s="21"/>
-      <c r="C136" s="21"/>
-      <c r="D136" s="22" t="s">
+      <c r="B136" s="26"/>
+      <c r="C136" s="26"/>
+      <c r="D136" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="E136" s="22"/>
-      <c r="F136" s="22"/>
+      <c r="E136" s="27"/>
+      <c r="F136" s="27"/>
       <c r="G136" s="8" t="s">
         <v>13</v>
       </c>
@@ -19642,16 +19632,16 @@
       </c>
     </row>
     <row r="137" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A137" s="21" t="s">
+      <c r="A137" s="26" t="s">
         <v>268</v>
       </c>
-      <c r="B137" s="21"/>
-      <c r="C137" s="21"/>
-      <c r="D137" s="22" t="s">
+      <c r="B137" s="26"/>
+      <c r="C137" s="26"/>
+      <c r="D137" s="27" t="s">
         <v>269</v>
       </c>
-      <c r="E137" s="22"/>
-      <c r="F137" s="22"/>
+      <c r="E137" s="27"/>
+      <c r="F137" s="27"/>
       <c r="G137" s="8" t="s">
         <v>13</v>
       </c>
@@ -19691,16 +19681,16 @@
       </c>
     </row>
     <row r="138" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A138" s="21" t="s">
+      <c r="A138" s="26" t="s">
         <v>270</v>
       </c>
-      <c r="B138" s="21"/>
-      <c r="C138" s="21"/>
-      <c r="D138" s="22" t="s">
+      <c r="B138" s="26"/>
+      <c r="C138" s="26"/>
+      <c r="D138" s="27" t="s">
         <v>271</v>
       </c>
-      <c r="E138" s="22"/>
-      <c r="F138" s="22"/>
+      <c r="E138" s="27"/>
+      <c r="F138" s="27"/>
       <c r="G138" s="8" t="s">
         <v>13</v>
       </c>
@@ -19738,16 +19728,16 @@
       </c>
     </row>
     <row r="139" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A139" s="21" t="s">
+      <c r="A139" s="26" t="s">
         <v>272</v>
       </c>
-      <c r="B139" s="21"/>
-      <c r="C139" s="21"/>
-      <c r="D139" s="22" t="s">
+      <c r="B139" s="26"/>
+      <c r="C139" s="26"/>
+      <c r="D139" s="27" t="s">
         <v>273</v>
       </c>
-      <c r="E139" s="22"/>
-      <c r="F139" s="22"/>
+      <c r="E139" s="27"/>
+      <c r="F139" s="27"/>
       <c r="G139" s="8" t="s">
         <v>13</v>
       </c>
@@ -19787,32 +19777,32 @@
       </c>
     </row>
     <row r="140" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="23" t="s">
+      <c r="A140" s="24" t="s">
         <v>274</v>
       </c>
-      <c r="B140" s="23"/>
-      <c r="C140" s="23"/>
-      <c r="D140" s="24" t="s">
+      <c r="B140" s="24"/>
+      <c r="C140" s="24"/>
+      <c r="D140" s="25" t="s">
         <v>275</v>
       </c>
-      <c r="E140" s="24"/>
-      <c r="F140" s="24"/>
+      <c r="E140" s="25"/>
+      <c r="F140" s="25"/>
       <c r="G140" s="5"/>
       <c r="H140" s="6"/>
       <c r="I140" s="7"/>
       <c r="J140" s="12"/>
     </row>
     <row r="141" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A141" s="21" t="s">
+      <c r="A141" s="26" t="s">
         <v>276</v>
       </c>
-      <c r="B141" s="21"/>
-      <c r="C141" s="21"/>
-      <c r="D141" s="22" t="s">
+      <c r="B141" s="26"/>
+      <c r="C141" s="26"/>
+      <c r="D141" s="27" t="s">
         <v>277</v>
       </c>
-      <c r="E141" s="22"/>
-      <c r="F141" s="22"/>
+      <c r="E141" s="27"/>
+      <c r="F141" s="27"/>
       <c r="G141" s="8" t="s">
         <v>13</v>
       </c>
@@ -19852,16 +19842,16 @@
       </c>
     </row>
     <row r="142" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A142" s="21" t="s">
+      <c r="A142" s="26" t="s">
         <v>278</v>
       </c>
-      <c r="B142" s="21"/>
-      <c r="C142" s="21"/>
-      <c r="D142" s="22" t="s">
+      <c r="B142" s="26"/>
+      <c r="C142" s="26"/>
+      <c r="D142" s="27" t="s">
         <v>279</v>
       </c>
-      <c r="E142" s="22"/>
-      <c r="F142" s="22"/>
+      <c r="E142" s="27"/>
+      <c r="F142" s="27"/>
       <c r="G142" s="8" t="s">
         <v>13</v>
       </c>
@@ -19901,16 +19891,16 @@
       </c>
     </row>
     <row r="143" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A143" s="21" t="s">
+      <c r="A143" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="B143" s="21"/>
-      <c r="C143" s="21"/>
-      <c r="D143" s="22" t="s">
+      <c r="B143" s="26"/>
+      <c r="C143" s="26"/>
+      <c r="D143" s="27" t="s">
         <v>281</v>
       </c>
-      <c r="E143" s="22"/>
-      <c r="F143" s="22"/>
+      <c r="E143" s="27"/>
+      <c r="F143" s="27"/>
       <c r="G143" s="8" t="s">
         <v>13</v>
       </c>
@@ -19950,16 +19940,16 @@
       </c>
     </row>
     <row r="144" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A144" s="21" t="s">
+      <c r="A144" s="26" t="s">
         <v>282</v>
       </c>
-      <c r="B144" s="21"/>
-      <c r="C144" s="21"/>
-      <c r="D144" s="22" t="s">
+      <c r="B144" s="26"/>
+      <c r="C144" s="26"/>
+      <c r="D144" s="27" t="s">
         <v>283</v>
       </c>
-      <c r="E144" s="22"/>
-      <c r="F144" s="22"/>
+      <c r="E144" s="27"/>
+      <c r="F144" s="27"/>
       <c r="G144" s="8" t="s">
         <v>13</v>
       </c>
@@ -19999,16 +19989,16 @@
       </c>
     </row>
     <row r="145" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A145" s="21" t="s">
+      <c r="A145" s="26" t="s">
         <v>284</v>
       </c>
-      <c r="B145" s="21"/>
-      <c r="C145" s="21"/>
-      <c r="D145" s="22" t="s">
+      <c r="B145" s="26"/>
+      <c r="C145" s="26"/>
+      <c r="D145" s="27" t="s">
         <v>285</v>
       </c>
-      <c r="E145" s="22"/>
-      <c r="F145" s="22"/>
+      <c r="E145" s="27"/>
+      <c r="F145" s="27"/>
       <c r="G145" s="8" t="s">
         <v>13</v>
       </c>
@@ -20046,16 +20036,16 @@
       </c>
     </row>
     <row r="146" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A146" s="21" t="s">
+      <c r="A146" s="26" t="s">
         <v>286</v>
       </c>
-      <c r="B146" s="21"/>
-      <c r="C146" s="21"/>
-      <c r="D146" s="22" t="s">
+      <c r="B146" s="26"/>
+      <c r="C146" s="26"/>
+      <c r="D146" s="27" t="s">
         <v>287</v>
       </c>
-      <c r="E146" s="22"/>
-      <c r="F146" s="22"/>
+      <c r="E146" s="27"/>
+      <c r="F146" s="27"/>
       <c r="G146" s="8" t="s">
         <v>13</v>
       </c>
@@ -20093,16 +20083,16 @@
       </c>
     </row>
     <row r="147" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A147" s="21" t="s">
+      <c r="A147" s="26" t="s">
         <v>288</v>
       </c>
-      <c r="B147" s="21"/>
-      <c r="C147" s="21"/>
-      <c r="D147" s="22" t="s">
+      <c r="B147" s="26"/>
+      <c r="C147" s="26"/>
+      <c r="D147" s="27" t="s">
         <v>289</v>
       </c>
-      <c r="E147" s="22"/>
-      <c r="F147" s="22"/>
+      <c r="E147" s="27"/>
+      <c r="F147" s="27"/>
       <c r="G147" s="8" t="s">
         <v>13</v>
       </c>
@@ -20142,16 +20132,16 @@
       </c>
     </row>
     <row r="148" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A148" s="21" t="s">
+      <c r="A148" s="26" t="s">
         <v>290</v>
       </c>
-      <c r="B148" s="21"/>
-      <c r="C148" s="21"/>
-      <c r="D148" s="22" t="s">
+      <c r="B148" s="26"/>
+      <c r="C148" s="26"/>
+      <c r="D148" s="27" t="s">
         <v>291</v>
       </c>
-      <c r="E148" s="22"/>
-      <c r="F148" s="22"/>
+      <c r="E148" s="27"/>
+      <c r="F148" s="27"/>
       <c r="G148" s="8" t="s">
         <v>13</v>
       </c>
@@ -20191,16 +20181,16 @@
       </c>
     </row>
     <row r="149" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A149" s="21" t="s">
+      <c r="A149" s="26" t="s">
         <v>292</v>
       </c>
-      <c r="B149" s="21"/>
-      <c r="C149" s="21"/>
-      <c r="D149" s="22" t="s">
+      <c r="B149" s="26"/>
+      <c r="C149" s="26"/>
+      <c r="D149" s="27" t="s">
         <v>293</v>
       </c>
-      <c r="E149" s="22"/>
-      <c r="F149" s="22"/>
+      <c r="E149" s="27"/>
+      <c r="F149" s="27"/>
       <c r="G149" s="8" t="s">
         <v>13</v>
       </c>
@@ -20238,16 +20228,16 @@
       </c>
     </row>
     <row r="150" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A150" s="21" t="s">
+      <c r="A150" s="26" t="s">
         <v>294</v>
       </c>
-      <c r="B150" s="21"/>
-      <c r="C150" s="21"/>
-      <c r="D150" s="22" t="s">
+      <c r="B150" s="26"/>
+      <c r="C150" s="26"/>
+      <c r="D150" s="27" t="s">
         <v>295</v>
       </c>
-      <c r="E150" s="22"/>
-      <c r="F150" s="22"/>
+      <c r="E150" s="27"/>
+      <c r="F150" s="27"/>
       <c r="G150" s="8" t="s">
         <v>13</v>
       </c>
@@ -20287,16 +20277,16 @@
       </c>
     </row>
     <row r="151" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A151" s="21" t="s">
+      <c r="A151" s="26" t="s">
         <v>296</v>
       </c>
-      <c r="B151" s="21"/>
-      <c r="C151" s="21"/>
-      <c r="D151" s="22" t="s">
+      <c r="B151" s="26"/>
+      <c r="C151" s="26"/>
+      <c r="D151" s="27" t="s">
         <v>297</v>
       </c>
-      <c r="E151" s="22"/>
-      <c r="F151" s="22"/>
+      <c r="E151" s="27"/>
+      <c r="F151" s="27"/>
       <c r="G151" s="8" t="s">
         <v>13</v>
       </c>
@@ -20336,16 +20326,16 @@
       </c>
     </row>
     <row r="152" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A152" s="21" t="s">
+      <c r="A152" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="B152" s="21"/>
-      <c r="C152" s="21"/>
-      <c r="D152" s="22" t="s">
+      <c r="B152" s="26"/>
+      <c r="C152" s="26"/>
+      <c r="D152" s="27" t="s">
         <v>299</v>
       </c>
-      <c r="E152" s="22"/>
-      <c r="F152" s="22"/>
+      <c r="E152" s="27"/>
+      <c r="F152" s="27"/>
       <c r="G152" s="8" t="s">
         <v>13</v>
       </c>
@@ -20385,16 +20375,16 @@
       </c>
     </row>
     <row r="153" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A153" s="21" t="s">
+      <c r="A153" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="B153" s="21"/>
-      <c r="C153" s="21"/>
-      <c r="D153" s="22" t="s">
+      <c r="B153" s="26"/>
+      <c r="C153" s="26"/>
+      <c r="D153" s="27" t="s">
         <v>301</v>
       </c>
-      <c r="E153" s="22"/>
-      <c r="F153" s="22"/>
+      <c r="E153" s="27"/>
+      <c r="F153" s="27"/>
       <c r="G153" s="8" t="s">
         <v>13</v>
       </c>
@@ -20434,16 +20424,16 @@
       </c>
     </row>
     <row r="154" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A154" s="21" t="s">
+      <c r="A154" s="26" t="s">
         <v>302</v>
       </c>
-      <c r="B154" s="21"/>
-      <c r="C154" s="21"/>
-      <c r="D154" s="22" t="s">
+      <c r="B154" s="26"/>
+      <c r="C154" s="26"/>
+      <c r="D154" s="27" t="s">
         <v>303</v>
       </c>
-      <c r="E154" s="22"/>
-      <c r="F154" s="22"/>
+      <c r="E154" s="27"/>
+      <c r="F154" s="27"/>
       <c r="G154" s="8" t="s">
         <v>13</v>
       </c>
@@ -20483,16 +20473,16 @@
       </c>
     </row>
     <row r="155" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A155" s="21" t="s">
+      <c r="A155" s="26" t="s">
         <v>304</v>
       </c>
-      <c r="B155" s="21"/>
-      <c r="C155" s="21"/>
-      <c r="D155" s="22" t="s">
+      <c r="B155" s="26"/>
+      <c r="C155" s="26"/>
+      <c r="D155" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="E155" s="22"/>
-      <c r="F155" s="22"/>
+      <c r="E155" s="27"/>
+      <c r="F155" s="27"/>
       <c r="G155" s="8" t="s">
         <v>13</v>
       </c>
@@ -20532,16 +20522,16 @@
       </c>
     </row>
     <row r="156" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A156" s="21" t="s">
+      <c r="A156" s="26" t="s">
         <v>306</v>
       </c>
-      <c r="B156" s="21"/>
-      <c r="C156" s="21"/>
-      <c r="D156" s="22" t="s">
+      <c r="B156" s="26"/>
+      <c r="C156" s="26"/>
+      <c r="D156" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="E156" s="22"/>
-      <c r="F156" s="22"/>
+      <c r="E156" s="27"/>
+      <c r="F156" s="27"/>
       <c r="G156" s="8" t="s">
         <v>13</v>
       </c>
@@ -20579,16 +20569,16 @@
       </c>
     </row>
     <row r="157" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A157" s="21" t="s">
+      <c r="A157" s="26" t="s">
         <v>308</v>
       </c>
-      <c r="B157" s="21"/>
-      <c r="C157" s="21"/>
-      <c r="D157" s="22" t="s">
+      <c r="B157" s="26"/>
+      <c r="C157" s="26"/>
+      <c r="D157" s="27" t="s">
         <v>309</v>
       </c>
-      <c r="E157" s="22"/>
-      <c r="F157" s="22"/>
+      <c r="E157" s="27"/>
+      <c r="F157" s="27"/>
       <c r="G157" s="8" t="s">
         <v>13</v>
       </c>
@@ -20628,16 +20618,16 @@
       </c>
     </row>
     <row r="158" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A158" s="21" t="s">
+      <c r="A158" s="26" t="s">
         <v>310</v>
       </c>
-      <c r="B158" s="21"/>
-      <c r="C158" s="21"/>
-      <c r="D158" s="22" t="s">
+      <c r="B158" s="26"/>
+      <c r="C158" s="26"/>
+      <c r="D158" s="27" t="s">
         <v>311</v>
       </c>
-      <c r="E158" s="22"/>
-      <c r="F158" s="22"/>
+      <c r="E158" s="27"/>
+      <c r="F158" s="27"/>
       <c r="G158" s="8" t="s">
         <v>13</v>
       </c>
@@ -20677,16 +20667,16 @@
       </c>
     </row>
     <row r="159" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A159" s="21" t="s">
+      <c r="A159" s="26" t="s">
         <v>312</v>
       </c>
-      <c r="B159" s="21"/>
-      <c r="C159" s="21"/>
-      <c r="D159" s="22" t="s">
+      <c r="B159" s="26"/>
+      <c r="C159" s="26"/>
+      <c r="D159" s="27" t="s">
         <v>313</v>
       </c>
-      <c r="E159" s="22"/>
-      <c r="F159" s="22"/>
+      <c r="E159" s="27"/>
+      <c r="F159" s="27"/>
       <c r="G159" s="8" t="s">
         <v>13</v>
       </c>
@@ -20726,16 +20716,16 @@
       </c>
     </row>
     <row r="160" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A160" s="21" t="s">
+      <c r="A160" s="26" t="s">
         <v>314</v>
       </c>
-      <c r="B160" s="21"/>
-      <c r="C160" s="21"/>
-      <c r="D160" s="22" t="s">
+      <c r="B160" s="26"/>
+      <c r="C160" s="26"/>
+      <c r="D160" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="E160" s="22"/>
-      <c r="F160" s="22"/>
+      <c r="E160" s="27"/>
+      <c r="F160" s="27"/>
       <c r="G160" s="8" t="s">
         <v>13</v>
       </c>
@@ -20775,16 +20765,16 @@
       </c>
     </row>
     <row r="161" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A161" s="21" t="s">
+      <c r="A161" s="26" t="s">
         <v>316</v>
       </c>
-      <c r="B161" s="21"/>
-      <c r="C161" s="21"/>
-      <c r="D161" s="22" t="s">
+      <c r="B161" s="26"/>
+      <c r="C161" s="26"/>
+      <c r="D161" s="27" t="s">
         <v>317</v>
       </c>
-      <c r="E161" s="22"/>
-      <c r="F161" s="22"/>
+      <c r="E161" s="27"/>
+      <c r="F161" s="27"/>
       <c r="G161" s="8" t="s">
         <v>13</v>
       </c>
@@ -20824,16 +20814,16 @@
       </c>
     </row>
     <row r="162" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A162" s="21" t="s">
+      <c r="A162" s="26" t="s">
         <v>318</v>
       </c>
-      <c r="B162" s="21"/>
-      <c r="C162" s="21"/>
-      <c r="D162" s="22" t="s">
+      <c r="B162" s="26"/>
+      <c r="C162" s="26"/>
+      <c r="D162" s="27" t="s">
         <v>319</v>
       </c>
-      <c r="E162" s="22"/>
-      <c r="F162" s="22"/>
+      <c r="E162" s="27"/>
+      <c r="F162" s="27"/>
       <c r="G162" s="8" t="s">
         <v>13</v>
       </c>
@@ -20873,16 +20863,16 @@
       </c>
     </row>
     <row r="163" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A163" s="21" t="s">
+      <c r="A163" s="26" t="s">
         <v>320</v>
       </c>
-      <c r="B163" s="21"/>
-      <c r="C163" s="21"/>
-      <c r="D163" s="22" t="s">
+      <c r="B163" s="26"/>
+      <c r="C163" s="26"/>
+      <c r="D163" s="27" t="s">
         <v>321</v>
       </c>
-      <c r="E163" s="22"/>
-      <c r="F163" s="22"/>
+      <c r="E163" s="27"/>
+      <c r="F163" s="27"/>
       <c r="G163" s="8" t="s">
         <v>13</v>
       </c>
@@ -20922,16 +20912,16 @@
       </c>
     </row>
     <row r="164" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A164" s="21" t="s">
+      <c r="A164" s="26" t="s">
         <v>322</v>
       </c>
-      <c r="B164" s="21"/>
-      <c r="C164" s="21"/>
-      <c r="D164" s="22" t="s">
+      <c r="B164" s="26"/>
+      <c r="C164" s="26"/>
+      <c r="D164" s="27" t="s">
         <v>323</v>
       </c>
-      <c r="E164" s="22"/>
-      <c r="F164" s="22"/>
+      <c r="E164" s="27"/>
+      <c r="F164" s="27"/>
       <c r="G164" s="8" t="s">
         <v>13</v>
       </c>
@@ -20971,16 +20961,16 @@
       </c>
     </row>
     <row r="165" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A165" s="21" t="s">
+      <c r="A165" s="26" t="s">
         <v>324</v>
       </c>
-      <c r="B165" s="21"/>
-      <c r="C165" s="21"/>
-      <c r="D165" s="22" t="s">
+      <c r="B165" s="26"/>
+      <c r="C165" s="26"/>
+      <c r="D165" s="27" t="s">
         <v>325</v>
       </c>
-      <c r="E165" s="22"/>
-      <c r="F165" s="22"/>
+      <c r="E165" s="27"/>
+      <c r="F165" s="27"/>
       <c r="G165" s="8" t="s">
         <v>13</v>
       </c>
@@ -21020,16 +21010,16 @@
       </c>
     </row>
     <row r="166" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A166" s="21" t="s">
+      <c r="A166" s="26" t="s">
         <v>326</v>
       </c>
-      <c r="B166" s="21"/>
-      <c r="C166" s="21"/>
-      <c r="D166" s="22" t="s">
+      <c r="B166" s="26"/>
+      <c r="C166" s="26"/>
+      <c r="D166" s="27" t="s">
         <v>327</v>
       </c>
-      <c r="E166" s="22"/>
-      <c r="F166" s="22"/>
+      <c r="E166" s="27"/>
+      <c r="F166" s="27"/>
       <c r="G166" s="8" t="s">
         <v>13</v>
       </c>
@@ -21067,16 +21057,16 @@
       </c>
     </row>
     <row r="167" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A167" s="21" t="s">
+      <c r="A167" s="26" t="s">
         <v>328</v>
       </c>
-      <c r="B167" s="21"/>
-      <c r="C167" s="21"/>
-      <c r="D167" s="22" t="s">
+      <c r="B167" s="26"/>
+      <c r="C167" s="26"/>
+      <c r="D167" s="27" t="s">
         <v>329</v>
       </c>
-      <c r="E167" s="22"/>
-      <c r="F167" s="22"/>
+      <c r="E167" s="27"/>
+      <c r="F167" s="27"/>
       <c r="G167" s="8" t="s">
         <v>13</v>
       </c>
@@ -21116,16 +21106,16 @@
       </c>
     </row>
     <row r="168" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A168" s="21" t="s">
+      <c r="A168" s="26" t="s">
         <v>330</v>
       </c>
-      <c r="B168" s="21"/>
-      <c r="C168" s="21"/>
-      <c r="D168" s="22" t="s">
+      <c r="B168" s="26"/>
+      <c r="C168" s="26"/>
+      <c r="D168" s="27" t="s">
         <v>331</v>
       </c>
-      <c r="E168" s="22"/>
-      <c r="F168" s="22"/>
+      <c r="E168" s="27"/>
+      <c r="F168" s="27"/>
       <c r="G168" s="8" t="s">
         <v>13</v>
       </c>
@@ -21163,16 +21153,16 @@
       </c>
     </row>
     <row r="169" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A169" s="21" t="s">
+      <c r="A169" s="26" t="s">
         <v>332</v>
       </c>
-      <c r="B169" s="21"/>
-      <c r="C169" s="21"/>
-      <c r="D169" s="22" t="s">
+      <c r="B169" s="26"/>
+      <c r="C169" s="26"/>
+      <c r="D169" s="27" t="s">
         <v>333</v>
       </c>
-      <c r="E169" s="22"/>
-      <c r="F169" s="22"/>
+      <c r="E169" s="27"/>
+      <c r="F169" s="27"/>
       <c r="G169" s="8" t="s">
         <v>13</v>
       </c>
@@ -21212,16 +21202,16 @@
       </c>
     </row>
     <row r="170" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A170" s="21" t="s">
+      <c r="A170" s="26" t="s">
         <v>334</v>
       </c>
-      <c r="B170" s="21"/>
-      <c r="C170" s="21"/>
-      <c r="D170" s="22" t="s">
+      <c r="B170" s="26"/>
+      <c r="C170" s="26"/>
+      <c r="D170" s="27" t="s">
         <v>335</v>
       </c>
-      <c r="E170" s="22"/>
-      <c r="F170" s="22"/>
+      <c r="E170" s="27"/>
+      <c r="F170" s="27"/>
       <c r="G170" s="8" t="s">
         <v>13</v>
       </c>
@@ -21261,16 +21251,16 @@
       </c>
     </row>
     <row r="171" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A171" s="21" t="s">
+      <c r="A171" s="26" t="s">
         <v>336</v>
       </c>
-      <c r="B171" s="21"/>
-      <c r="C171" s="21"/>
-      <c r="D171" s="22" t="s">
+      <c r="B171" s="26"/>
+      <c r="C171" s="26"/>
+      <c r="D171" s="27" t="s">
         <v>337</v>
       </c>
-      <c r="E171" s="22"/>
-      <c r="F171" s="22"/>
+      <c r="E171" s="27"/>
+      <c r="F171" s="27"/>
       <c r="G171" s="8" t="s">
         <v>13</v>
       </c>
@@ -21308,16 +21298,16 @@
       </c>
     </row>
     <row r="172" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A172" s="21" t="s">
+      <c r="A172" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="B172" s="21"/>
-      <c r="C172" s="21"/>
-      <c r="D172" s="22" t="s">
+      <c r="B172" s="26"/>
+      <c r="C172" s="26"/>
+      <c r="D172" s="27" t="s">
         <v>339</v>
       </c>
-      <c r="E172" s="22"/>
-      <c r="F172" s="22"/>
+      <c r="E172" s="27"/>
+      <c r="F172" s="27"/>
       <c r="G172" s="8" t="s">
         <v>13</v>
       </c>
@@ -21357,16 +21347,16 @@
       </c>
     </row>
     <row r="173" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A173" s="21" t="s">
+      <c r="A173" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="B173" s="21"/>
-      <c r="C173" s="21"/>
-      <c r="D173" s="22" t="s">
+      <c r="B173" s="26"/>
+      <c r="C173" s="26"/>
+      <c r="D173" s="27" t="s">
         <v>341</v>
       </c>
-      <c r="E173" s="22"/>
-      <c r="F173" s="22"/>
+      <c r="E173" s="27"/>
+      <c r="F173" s="27"/>
       <c r="G173" s="8" t="s">
         <v>12</v>
       </c>
@@ -21406,16 +21396,16 @@
       </c>
     </row>
     <row r="174" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A174" s="21" t="s">
+      <c r="A174" s="26" t="s">
         <v>342</v>
       </c>
-      <c r="B174" s="21"/>
-      <c r="C174" s="21"/>
-      <c r="D174" s="22" t="s">
+      <c r="B174" s="26"/>
+      <c r="C174" s="26"/>
+      <c r="D174" s="27" t="s">
         <v>343</v>
       </c>
-      <c r="E174" s="22"/>
-      <c r="F174" s="22"/>
+      <c r="E174" s="27"/>
+      <c r="F174" s="27"/>
       <c r="G174" s="8" t="s">
         <v>13</v>
       </c>
@@ -21455,16 +21445,16 @@
       </c>
     </row>
     <row r="175" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A175" s="21" t="s">
+      <c r="A175" s="26" t="s">
         <v>344</v>
       </c>
-      <c r="B175" s="21"/>
-      <c r="C175" s="21"/>
-      <c r="D175" s="22" t="s">
+      <c r="B175" s="26"/>
+      <c r="C175" s="26"/>
+      <c r="D175" s="27" t="s">
         <v>345</v>
       </c>
-      <c r="E175" s="22"/>
-      <c r="F175" s="22"/>
+      <c r="E175" s="27"/>
+      <c r="F175" s="27"/>
       <c r="G175" s="8" t="s">
         <v>13</v>
       </c>
@@ -21504,16 +21494,16 @@
       </c>
     </row>
     <row r="176" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A176" s="21" t="s">
+      <c r="A176" s="26" t="s">
         <v>346</v>
       </c>
-      <c r="B176" s="21"/>
-      <c r="C176" s="21"/>
-      <c r="D176" s="22" t="s">
+      <c r="B176" s="26"/>
+      <c r="C176" s="26"/>
+      <c r="D176" s="27" t="s">
         <v>347</v>
       </c>
-      <c r="E176" s="22"/>
-      <c r="F176" s="22"/>
+      <c r="E176" s="27"/>
+      <c r="F176" s="27"/>
       <c r="G176" s="8" t="s">
         <v>13</v>
       </c>
@@ -21553,16 +21543,16 @@
       </c>
     </row>
     <row r="177" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A177" s="21" t="s">
+      <c r="A177" s="26" t="s">
         <v>348</v>
       </c>
-      <c r="B177" s="21"/>
-      <c r="C177" s="21"/>
-      <c r="D177" s="22" t="s">
+      <c r="B177" s="26"/>
+      <c r="C177" s="26"/>
+      <c r="D177" s="27" t="s">
         <v>349</v>
       </c>
-      <c r="E177" s="22"/>
-      <c r="F177" s="22"/>
+      <c r="E177" s="27"/>
+      <c r="F177" s="27"/>
       <c r="G177" s="8" t="s">
         <v>13</v>
       </c>
@@ -21602,16 +21592,16 @@
       </c>
     </row>
     <row r="178" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A178" s="21" t="s">
+      <c r="A178" s="26" t="s">
         <v>350</v>
       </c>
-      <c r="B178" s="21"/>
-      <c r="C178" s="21"/>
-      <c r="D178" s="22" t="s">
+      <c r="B178" s="26"/>
+      <c r="C178" s="26"/>
+      <c r="D178" s="27" t="s">
         <v>351</v>
       </c>
-      <c r="E178" s="22"/>
-      <c r="F178" s="22"/>
+      <c r="E178" s="27"/>
+      <c r="F178" s="27"/>
       <c r="G178" s="8" t="s">
         <v>13</v>
       </c>
@@ -21651,16 +21641,16 @@
       </c>
     </row>
     <row r="179" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A179" s="21" t="s">
+      <c r="A179" s="26" t="s">
         <v>352</v>
       </c>
-      <c r="B179" s="21"/>
-      <c r="C179" s="21"/>
-      <c r="D179" s="22" t="s">
+      <c r="B179" s="26"/>
+      <c r="C179" s="26"/>
+      <c r="D179" s="27" t="s">
         <v>353</v>
       </c>
-      <c r="E179" s="22"/>
-      <c r="F179" s="22"/>
+      <c r="E179" s="27"/>
+      <c r="F179" s="27"/>
       <c r="G179" s="8" t="s">
         <v>13</v>
       </c>
@@ -21700,16 +21690,16 @@
       </c>
     </row>
     <row r="180" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A180" s="21" t="s">
+      <c r="A180" s="26" t="s">
         <v>354</v>
       </c>
-      <c r="B180" s="21"/>
-      <c r="C180" s="21"/>
-      <c r="D180" s="22" t="s">
+      <c r="B180" s="26"/>
+      <c r="C180" s="26"/>
+      <c r="D180" s="27" t="s">
         <v>355</v>
       </c>
-      <c r="E180" s="22"/>
-      <c r="F180" s="22"/>
+      <c r="E180" s="27"/>
+      <c r="F180" s="27"/>
       <c r="G180" s="8" t="s">
         <v>13</v>
       </c>
@@ -21749,16 +21739,16 @@
       </c>
     </row>
     <row r="181" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A181" s="21" t="s">
+      <c r="A181" s="26" t="s">
         <v>356</v>
       </c>
-      <c r="B181" s="21"/>
-      <c r="C181" s="21"/>
-      <c r="D181" s="22" t="s">
+      <c r="B181" s="26"/>
+      <c r="C181" s="26"/>
+      <c r="D181" s="27" t="s">
         <v>357</v>
       </c>
-      <c r="E181" s="22"/>
-      <c r="F181" s="22"/>
+      <c r="E181" s="27"/>
+      <c r="F181" s="27"/>
       <c r="G181" s="8" t="s">
         <v>13</v>
       </c>
@@ -21798,16 +21788,16 @@
       </c>
     </row>
     <row r="182" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A182" s="21" t="s">
+      <c r="A182" s="26" t="s">
         <v>358</v>
       </c>
-      <c r="B182" s="21"/>
-      <c r="C182" s="21"/>
-      <c r="D182" s="22" t="s">
+      <c r="B182" s="26"/>
+      <c r="C182" s="26"/>
+      <c r="D182" s="27" t="s">
         <v>359</v>
       </c>
-      <c r="E182" s="22"/>
-      <c r="F182" s="22"/>
+      <c r="E182" s="27"/>
+      <c r="F182" s="27"/>
       <c r="G182" s="8" t="s">
         <v>12</v>
       </c>
@@ -21847,16 +21837,16 @@
       </c>
     </row>
     <row r="183" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A183" s="21" t="s">
+      <c r="A183" s="26" t="s">
         <v>360</v>
       </c>
-      <c r="B183" s="21"/>
-      <c r="C183" s="21"/>
-      <c r="D183" s="22" t="s">
+      <c r="B183" s="26"/>
+      <c r="C183" s="26"/>
+      <c r="D183" s="27" t="s">
         <v>361</v>
       </c>
-      <c r="E183" s="22"/>
-      <c r="F183" s="22"/>
+      <c r="E183" s="27"/>
+      <c r="F183" s="27"/>
       <c r="G183" s="8" t="s">
         <v>13</v>
       </c>
@@ -21896,16 +21886,16 @@
       </c>
     </row>
     <row r="184" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A184" s="21" t="s">
+      <c r="A184" s="26" t="s">
         <v>362</v>
       </c>
-      <c r="B184" s="21"/>
-      <c r="C184" s="21"/>
-      <c r="D184" s="22" t="s">
+      <c r="B184" s="26"/>
+      <c r="C184" s="26"/>
+      <c r="D184" s="27" t="s">
         <v>363</v>
       </c>
-      <c r="E184" s="22"/>
-      <c r="F184" s="22"/>
+      <c r="E184" s="27"/>
+      <c r="F184" s="27"/>
       <c r="G184" s="8" t="s">
         <v>13</v>
       </c>
@@ -21945,16 +21935,16 @@
       </c>
     </row>
     <row r="185" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A185" s="21" t="s">
+      <c r="A185" s="26" t="s">
         <v>364</v>
       </c>
-      <c r="B185" s="21"/>
-      <c r="C185" s="21"/>
-      <c r="D185" s="22" t="s">
+      <c r="B185" s="26"/>
+      <c r="C185" s="26"/>
+      <c r="D185" s="27" t="s">
         <v>365</v>
       </c>
-      <c r="E185" s="22"/>
-      <c r="F185" s="22"/>
+      <c r="E185" s="27"/>
+      <c r="F185" s="27"/>
       <c r="G185" s="8" t="s">
         <v>13</v>
       </c>
@@ -21992,16 +21982,16 @@
       </c>
     </row>
     <row r="186" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A186" s="21" t="s">
+      <c r="A186" s="26" t="s">
         <v>366</v>
       </c>
-      <c r="B186" s="21"/>
-      <c r="C186" s="21"/>
-      <c r="D186" s="22" t="s">
+      <c r="B186" s="26"/>
+      <c r="C186" s="26"/>
+      <c r="D186" s="27" t="s">
         <v>367</v>
       </c>
-      <c r="E186" s="22"/>
-      <c r="F186" s="22"/>
+      <c r="E186" s="27"/>
+      <c r="F186" s="27"/>
       <c r="G186" s="8" t="s">
         <v>13</v>
       </c>
@@ -22041,16 +22031,16 @@
       </c>
     </row>
     <row r="187" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A187" s="21" t="s">
+      <c r="A187" s="26" t="s">
         <v>368</v>
       </c>
-      <c r="B187" s="21"/>
-      <c r="C187" s="21"/>
-      <c r="D187" s="22" t="s">
+      <c r="B187" s="26"/>
+      <c r="C187" s="26"/>
+      <c r="D187" s="27" t="s">
         <v>369</v>
       </c>
-      <c r="E187" s="22"/>
-      <c r="F187" s="22"/>
+      <c r="E187" s="27"/>
+      <c r="F187" s="27"/>
       <c r="G187" s="8" t="s">
         <v>13</v>
       </c>
@@ -22090,16 +22080,16 @@
       </c>
     </row>
     <row r="188" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A188" s="21" t="s">
+      <c r="A188" s="26" t="s">
         <v>370</v>
       </c>
-      <c r="B188" s="21"/>
-      <c r="C188" s="21"/>
-      <c r="D188" s="22" t="s">
+      <c r="B188" s="26"/>
+      <c r="C188" s="26"/>
+      <c r="D188" s="27" t="s">
         <v>371</v>
       </c>
-      <c r="E188" s="22"/>
-      <c r="F188" s="22"/>
+      <c r="E188" s="27"/>
+      <c r="F188" s="27"/>
       <c r="G188" s="8" t="s">
         <v>13</v>
       </c>
@@ -22139,16 +22129,16 @@
       </c>
     </row>
     <row r="189" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A189" s="21" t="s">
+      <c r="A189" s="26" t="s">
         <v>372</v>
       </c>
-      <c r="B189" s="21"/>
-      <c r="C189" s="21"/>
-      <c r="D189" s="22" t="s">
+      <c r="B189" s="26"/>
+      <c r="C189" s="26"/>
+      <c r="D189" s="27" t="s">
         <v>373</v>
       </c>
-      <c r="E189" s="22"/>
-      <c r="F189" s="22"/>
+      <c r="E189" s="27"/>
+      <c r="F189" s="27"/>
       <c r="G189" s="8" t="s">
         <v>13</v>
       </c>
@@ -22188,16 +22178,16 @@
       </c>
     </row>
     <row r="190" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A190" s="21" t="s">
+      <c r="A190" s="26" t="s">
         <v>374</v>
       </c>
-      <c r="B190" s="21"/>
-      <c r="C190" s="21"/>
-      <c r="D190" s="22" t="s">
+      <c r="B190" s="26"/>
+      <c r="C190" s="26"/>
+      <c r="D190" s="27" t="s">
         <v>375</v>
       </c>
-      <c r="E190" s="22"/>
-      <c r="F190" s="22"/>
+      <c r="E190" s="27"/>
+      <c r="F190" s="27"/>
       <c r="G190" s="8" t="s">
         <v>13</v>
       </c>
@@ -22237,16 +22227,16 @@
       </c>
     </row>
     <row r="191" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A191" s="21" t="s">
+      <c r="A191" s="26" t="s">
         <v>376</v>
       </c>
-      <c r="B191" s="21"/>
-      <c r="C191" s="21"/>
-      <c r="D191" s="22" t="s">
+      <c r="B191" s="26"/>
+      <c r="C191" s="26"/>
+      <c r="D191" s="27" t="s">
         <v>377</v>
       </c>
-      <c r="E191" s="22"/>
-      <c r="F191" s="22"/>
+      <c r="E191" s="27"/>
+      <c r="F191" s="27"/>
       <c r="G191" s="8" t="s">
         <v>13</v>
       </c>
@@ -22286,16 +22276,16 @@
       </c>
     </row>
     <row r="192" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A192" s="21" t="s">
+      <c r="A192" s="26" t="s">
         <v>378</v>
       </c>
-      <c r="B192" s="21"/>
-      <c r="C192" s="21"/>
-      <c r="D192" s="22" t="s">
+      <c r="B192" s="26"/>
+      <c r="C192" s="26"/>
+      <c r="D192" s="27" t="s">
         <v>379</v>
       </c>
-      <c r="E192" s="22"/>
-      <c r="F192" s="22"/>
+      <c r="E192" s="27"/>
+      <c r="F192" s="27"/>
       <c r="G192" s="8" t="s">
         <v>13</v>
       </c>
@@ -22335,16 +22325,16 @@
       </c>
     </row>
     <row r="193" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A193" s="21" t="s">
+      <c r="A193" s="26" t="s">
         <v>380</v>
       </c>
-      <c r="B193" s="21"/>
-      <c r="C193" s="21"/>
-      <c r="D193" s="22" t="s">
+      <c r="B193" s="26"/>
+      <c r="C193" s="26"/>
+      <c r="D193" s="27" t="s">
         <v>381</v>
       </c>
-      <c r="E193" s="22"/>
-      <c r="F193" s="22"/>
+      <c r="E193" s="27"/>
+      <c r="F193" s="27"/>
       <c r="G193" s="8" t="s">
         <v>13</v>
       </c>
@@ -22382,16 +22372,16 @@
       </c>
     </row>
     <row r="194" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A194" s="21" t="s">
+      <c r="A194" s="26" t="s">
         <v>382</v>
       </c>
-      <c r="B194" s="21"/>
-      <c r="C194" s="21"/>
-      <c r="D194" s="22" t="s">
+      <c r="B194" s="26"/>
+      <c r="C194" s="26"/>
+      <c r="D194" s="27" t="s">
         <v>383</v>
       </c>
-      <c r="E194" s="22"/>
-      <c r="F194" s="22"/>
+      <c r="E194" s="27"/>
+      <c r="F194" s="27"/>
       <c r="G194" s="8" t="s">
         <v>13</v>
       </c>
@@ -22431,16 +22421,16 @@
       </c>
     </row>
     <row r="195" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A195" s="21" t="s">
+      <c r="A195" s="26" t="s">
         <v>384</v>
       </c>
-      <c r="B195" s="21"/>
-      <c r="C195" s="21"/>
-      <c r="D195" s="22" t="s">
+      <c r="B195" s="26"/>
+      <c r="C195" s="26"/>
+      <c r="D195" s="27" t="s">
         <v>385</v>
       </c>
-      <c r="E195" s="22"/>
-      <c r="F195" s="22"/>
+      <c r="E195" s="27"/>
+      <c r="F195" s="27"/>
       <c r="G195" s="8" t="s">
         <v>13</v>
       </c>
@@ -22480,16 +22470,16 @@
       </c>
     </row>
     <row r="196" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A196" s="21" t="s">
+      <c r="A196" s="26" t="s">
         <v>386</v>
       </c>
-      <c r="B196" s="21"/>
-      <c r="C196" s="21"/>
-      <c r="D196" s="22" t="s">
+      <c r="B196" s="26"/>
+      <c r="C196" s="26"/>
+      <c r="D196" s="27" t="s">
         <v>387</v>
       </c>
-      <c r="E196" s="22"/>
-      <c r="F196" s="22"/>
+      <c r="E196" s="27"/>
+      <c r="F196" s="27"/>
       <c r="G196" s="8" t="s">
         <v>13</v>
       </c>
@@ -22529,16 +22519,16 @@
       </c>
     </row>
     <row r="197" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A197" s="21" t="s">
+      <c r="A197" s="26" t="s">
         <v>388</v>
       </c>
-      <c r="B197" s="21"/>
-      <c r="C197" s="21"/>
-      <c r="D197" s="22" t="s">
+      <c r="B197" s="26"/>
+      <c r="C197" s="26"/>
+      <c r="D197" s="27" t="s">
         <v>389</v>
       </c>
-      <c r="E197" s="22"/>
-      <c r="F197" s="22"/>
+      <c r="E197" s="27"/>
+      <c r="F197" s="27"/>
       <c r="G197" s="8" t="s">
         <v>13</v>
       </c>
@@ -22576,16 +22566,16 @@
       </c>
     </row>
     <row r="198" spans="1:16" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A198" s="21" t="s">
+      <c r="A198" s="26" t="s">
         <v>390</v>
       </c>
-      <c r="B198" s="21"/>
-      <c r="C198" s="21"/>
-      <c r="D198" s="22" t="s">
+      <c r="B198" s="26"/>
+      <c r="C198" s="26"/>
+      <c r="D198" s="27" t="s">
         <v>391</v>
       </c>
-      <c r="E198" s="22"/>
-      <c r="F198" s="22"/>
+      <c r="E198" s="27"/>
+      <c r="F198" s="27"/>
       <c r="G198" s="8" t="s">
         <v>13</v>
       </c>
@@ -22630,367 +22620,6 @@
     <filterColumn colId="4" showButton="0"/>
   </autoFilter>
   <mergeCells count="385">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="A66:C66"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="A70:C70"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="A71:C71"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="D72:F72"/>
-    <mergeCell ref="A73:C73"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="A74:C74"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="A76:C76"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="A77:C77"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="A78:C78"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="A79:C79"/>
-    <mergeCell ref="D79:F79"/>
-    <mergeCell ref="A80:C80"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="A81:C81"/>
-    <mergeCell ref="D81:F81"/>
-    <mergeCell ref="A82:C82"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="A83:C83"/>
-    <mergeCell ref="D83:F83"/>
-    <mergeCell ref="A84:C84"/>
-    <mergeCell ref="D84:F84"/>
-    <mergeCell ref="A85:C85"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="A86:C86"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="A87:C87"/>
-    <mergeCell ref="D87:F87"/>
-    <mergeCell ref="A88:C88"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="A89:C89"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="A90:C90"/>
-    <mergeCell ref="D90:F90"/>
-    <mergeCell ref="A91:C91"/>
-    <mergeCell ref="D91:F91"/>
-    <mergeCell ref="A92:C92"/>
-    <mergeCell ref="D92:F92"/>
-    <mergeCell ref="A93:C93"/>
-    <mergeCell ref="D93:F93"/>
-    <mergeCell ref="A94:C94"/>
-    <mergeCell ref="D94:F94"/>
-    <mergeCell ref="A95:C95"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="A96:C96"/>
-    <mergeCell ref="D96:F96"/>
-    <mergeCell ref="A97:C97"/>
-    <mergeCell ref="D97:F97"/>
-    <mergeCell ref="A98:C98"/>
-    <mergeCell ref="D98:F98"/>
-    <mergeCell ref="A99:C99"/>
-    <mergeCell ref="D99:F99"/>
-    <mergeCell ref="A100:C100"/>
-    <mergeCell ref="D100:F100"/>
-    <mergeCell ref="A101:C101"/>
-    <mergeCell ref="D101:F101"/>
-    <mergeCell ref="A102:C102"/>
-    <mergeCell ref="D102:F102"/>
-    <mergeCell ref="A103:C103"/>
-    <mergeCell ref="D103:F103"/>
-    <mergeCell ref="A104:C104"/>
-    <mergeCell ref="D104:F104"/>
-    <mergeCell ref="A105:C105"/>
-    <mergeCell ref="D105:F105"/>
-    <mergeCell ref="A106:C106"/>
-    <mergeCell ref="D106:F106"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="D107:F107"/>
-    <mergeCell ref="A108:C108"/>
-    <mergeCell ref="D108:F108"/>
-    <mergeCell ref="A109:C109"/>
-    <mergeCell ref="D109:F109"/>
-    <mergeCell ref="A110:C110"/>
-    <mergeCell ref="D110:F110"/>
-    <mergeCell ref="A111:C111"/>
-    <mergeCell ref="D111:F111"/>
-    <mergeCell ref="A112:C112"/>
-    <mergeCell ref="D112:F112"/>
-    <mergeCell ref="A113:C113"/>
-    <mergeCell ref="D113:F113"/>
-    <mergeCell ref="A114:C114"/>
-    <mergeCell ref="D114:F114"/>
-    <mergeCell ref="A115:C115"/>
-    <mergeCell ref="D115:F115"/>
-    <mergeCell ref="A116:C116"/>
-    <mergeCell ref="D116:F116"/>
-    <mergeCell ref="A117:C117"/>
-    <mergeCell ref="D117:F117"/>
-    <mergeCell ref="A118:C118"/>
-    <mergeCell ref="D118:F118"/>
-    <mergeCell ref="A119:C119"/>
-    <mergeCell ref="D119:F119"/>
-    <mergeCell ref="A120:C120"/>
-    <mergeCell ref="D120:F120"/>
-    <mergeCell ref="A121:C121"/>
-    <mergeCell ref="D121:F121"/>
-    <mergeCell ref="A122:C122"/>
-    <mergeCell ref="D122:F122"/>
-    <mergeCell ref="A123:C123"/>
-    <mergeCell ref="D123:F123"/>
-    <mergeCell ref="A124:C124"/>
-    <mergeCell ref="D124:F124"/>
-    <mergeCell ref="A125:C125"/>
-    <mergeCell ref="D125:F125"/>
-    <mergeCell ref="A126:C126"/>
-    <mergeCell ref="D126:F126"/>
-    <mergeCell ref="A127:C127"/>
-    <mergeCell ref="D127:F127"/>
-    <mergeCell ref="A128:C128"/>
-    <mergeCell ref="D128:F128"/>
-    <mergeCell ref="A129:C129"/>
-    <mergeCell ref="D129:F129"/>
-    <mergeCell ref="A130:C130"/>
-    <mergeCell ref="D130:F130"/>
-    <mergeCell ref="A131:C131"/>
-    <mergeCell ref="D131:F131"/>
-    <mergeCell ref="A132:C132"/>
-    <mergeCell ref="D132:F132"/>
-    <mergeCell ref="A133:C133"/>
-    <mergeCell ref="D133:F133"/>
-    <mergeCell ref="A134:C134"/>
-    <mergeCell ref="D134:F134"/>
-    <mergeCell ref="A135:C135"/>
-    <mergeCell ref="D135:F135"/>
-    <mergeCell ref="A136:C136"/>
-    <mergeCell ref="D136:F136"/>
-    <mergeCell ref="A137:C137"/>
-    <mergeCell ref="D137:F137"/>
-    <mergeCell ref="A138:C138"/>
-    <mergeCell ref="D138:F138"/>
-    <mergeCell ref="A139:C139"/>
-    <mergeCell ref="D139:F139"/>
-    <mergeCell ref="A140:C140"/>
-    <mergeCell ref="D140:F140"/>
-    <mergeCell ref="A141:C141"/>
-    <mergeCell ref="D141:F141"/>
-    <mergeCell ref="A142:C142"/>
-    <mergeCell ref="D142:F142"/>
-    <mergeCell ref="A143:C143"/>
-    <mergeCell ref="D143:F143"/>
-    <mergeCell ref="A144:C144"/>
-    <mergeCell ref="D144:F144"/>
-    <mergeCell ref="A145:C145"/>
-    <mergeCell ref="D145:F145"/>
-    <mergeCell ref="A146:C146"/>
-    <mergeCell ref="D146:F146"/>
-    <mergeCell ref="A147:C147"/>
-    <mergeCell ref="D147:F147"/>
-    <mergeCell ref="A148:C148"/>
-    <mergeCell ref="D148:F148"/>
-    <mergeCell ref="A149:C149"/>
-    <mergeCell ref="D149:F149"/>
-    <mergeCell ref="A150:C150"/>
-    <mergeCell ref="D150:F150"/>
-    <mergeCell ref="A151:C151"/>
-    <mergeCell ref="D151:F151"/>
-    <mergeCell ref="A152:C152"/>
-    <mergeCell ref="D152:F152"/>
-    <mergeCell ref="A153:C153"/>
-    <mergeCell ref="D153:F153"/>
-    <mergeCell ref="A154:C154"/>
-    <mergeCell ref="D154:F154"/>
-    <mergeCell ref="A155:C155"/>
-    <mergeCell ref="D155:F155"/>
-    <mergeCell ref="A156:C156"/>
-    <mergeCell ref="D156:F156"/>
-    <mergeCell ref="A157:C157"/>
-    <mergeCell ref="D157:F157"/>
-    <mergeCell ref="A158:C158"/>
-    <mergeCell ref="D158:F158"/>
-    <mergeCell ref="A159:C159"/>
-    <mergeCell ref="D159:F159"/>
-    <mergeCell ref="A160:C160"/>
-    <mergeCell ref="D160:F160"/>
-    <mergeCell ref="A161:C161"/>
-    <mergeCell ref="D161:F161"/>
-    <mergeCell ref="A162:C162"/>
-    <mergeCell ref="D162:F162"/>
-    <mergeCell ref="A163:C163"/>
-    <mergeCell ref="D163:F163"/>
-    <mergeCell ref="A164:C164"/>
-    <mergeCell ref="D164:F164"/>
-    <mergeCell ref="A165:C165"/>
-    <mergeCell ref="D165:F165"/>
-    <mergeCell ref="A166:C166"/>
-    <mergeCell ref="D166:F166"/>
-    <mergeCell ref="A167:C167"/>
-    <mergeCell ref="D167:F167"/>
-    <mergeCell ref="A168:C168"/>
-    <mergeCell ref="D168:F168"/>
-    <mergeCell ref="A169:C169"/>
-    <mergeCell ref="D169:F169"/>
-    <mergeCell ref="A170:C170"/>
-    <mergeCell ref="D170:F170"/>
-    <mergeCell ref="A171:C171"/>
-    <mergeCell ref="D171:F171"/>
-    <mergeCell ref="A172:C172"/>
-    <mergeCell ref="D172:F172"/>
-    <mergeCell ref="A173:C173"/>
-    <mergeCell ref="D173:F173"/>
-    <mergeCell ref="A181:C181"/>
-    <mergeCell ref="D181:F181"/>
-    <mergeCell ref="A182:C182"/>
-    <mergeCell ref="D182:F182"/>
-    <mergeCell ref="A183:C183"/>
-    <mergeCell ref="D183:F183"/>
-    <mergeCell ref="A174:C174"/>
-    <mergeCell ref="D174:F174"/>
-    <mergeCell ref="A175:C175"/>
-    <mergeCell ref="D175:F175"/>
-    <mergeCell ref="A176:C176"/>
-    <mergeCell ref="D176:F176"/>
-    <mergeCell ref="A177:C177"/>
-    <mergeCell ref="D177:F177"/>
-    <mergeCell ref="A178:C178"/>
-    <mergeCell ref="D178:F178"/>
-    <mergeCell ref="A198:C198"/>
-    <mergeCell ref="D198:F198"/>
-    <mergeCell ref="A189:C189"/>
-    <mergeCell ref="D189:F189"/>
-    <mergeCell ref="A190:C190"/>
-    <mergeCell ref="D190:F190"/>
-    <mergeCell ref="A191:C191"/>
-    <mergeCell ref="D191:F191"/>
-    <mergeCell ref="A192:C192"/>
-    <mergeCell ref="D192:F192"/>
-    <mergeCell ref="A193:C193"/>
-    <mergeCell ref="D193:F193"/>
     <mergeCell ref="M5:N5"/>
     <mergeCell ref="O6:P6"/>
     <mergeCell ref="A194:C194"/>
@@ -23015,6 +22644,367 @@
     <mergeCell ref="D179:F179"/>
     <mergeCell ref="A180:C180"/>
     <mergeCell ref="D180:F180"/>
+    <mergeCell ref="A198:C198"/>
+    <mergeCell ref="D198:F198"/>
+    <mergeCell ref="A189:C189"/>
+    <mergeCell ref="D189:F189"/>
+    <mergeCell ref="A190:C190"/>
+    <mergeCell ref="D190:F190"/>
+    <mergeCell ref="A191:C191"/>
+    <mergeCell ref="D191:F191"/>
+    <mergeCell ref="A192:C192"/>
+    <mergeCell ref="D192:F192"/>
+    <mergeCell ref="A193:C193"/>
+    <mergeCell ref="D193:F193"/>
+    <mergeCell ref="A181:C181"/>
+    <mergeCell ref="D181:F181"/>
+    <mergeCell ref="A182:C182"/>
+    <mergeCell ref="D182:F182"/>
+    <mergeCell ref="A183:C183"/>
+    <mergeCell ref="D183:F183"/>
+    <mergeCell ref="A174:C174"/>
+    <mergeCell ref="D174:F174"/>
+    <mergeCell ref="A175:C175"/>
+    <mergeCell ref="D175:F175"/>
+    <mergeCell ref="A176:C176"/>
+    <mergeCell ref="D176:F176"/>
+    <mergeCell ref="A177:C177"/>
+    <mergeCell ref="D177:F177"/>
+    <mergeCell ref="A178:C178"/>
+    <mergeCell ref="D178:F178"/>
+    <mergeCell ref="A169:C169"/>
+    <mergeCell ref="D169:F169"/>
+    <mergeCell ref="A170:C170"/>
+    <mergeCell ref="D170:F170"/>
+    <mergeCell ref="A171:C171"/>
+    <mergeCell ref="D171:F171"/>
+    <mergeCell ref="A172:C172"/>
+    <mergeCell ref="D172:F172"/>
+    <mergeCell ref="A173:C173"/>
+    <mergeCell ref="D173:F173"/>
+    <mergeCell ref="A164:C164"/>
+    <mergeCell ref="D164:F164"/>
+    <mergeCell ref="A165:C165"/>
+    <mergeCell ref="D165:F165"/>
+    <mergeCell ref="A166:C166"/>
+    <mergeCell ref="D166:F166"/>
+    <mergeCell ref="A167:C167"/>
+    <mergeCell ref="D167:F167"/>
+    <mergeCell ref="A168:C168"/>
+    <mergeCell ref="D168:F168"/>
+    <mergeCell ref="A159:C159"/>
+    <mergeCell ref="D159:F159"/>
+    <mergeCell ref="A160:C160"/>
+    <mergeCell ref="D160:F160"/>
+    <mergeCell ref="A161:C161"/>
+    <mergeCell ref="D161:F161"/>
+    <mergeCell ref="A162:C162"/>
+    <mergeCell ref="D162:F162"/>
+    <mergeCell ref="A163:C163"/>
+    <mergeCell ref="D163:F163"/>
+    <mergeCell ref="A154:C154"/>
+    <mergeCell ref="D154:F154"/>
+    <mergeCell ref="A155:C155"/>
+    <mergeCell ref="D155:F155"/>
+    <mergeCell ref="A156:C156"/>
+    <mergeCell ref="D156:F156"/>
+    <mergeCell ref="A157:C157"/>
+    <mergeCell ref="D157:F157"/>
+    <mergeCell ref="A158:C158"/>
+    <mergeCell ref="D158:F158"/>
+    <mergeCell ref="A149:C149"/>
+    <mergeCell ref="D149:F149"/>
+    <mergeCell ref="A150:C150"/>
+    <mergeCell ref="D150:F150"/>
+    <mergeCell ref="A151:C151"/>
+    <mergeCell ref="D151:F151"/>
+    <mergeCell ref="A152:C152"/>
+    <mergeCell ref="D152:F152"/>
+    <mergeCell ref="A153:C153"/>
+    <mergeCell ref="D153:F153"/>
+    <mergeCell ref="A144:C144"/>
+    <mergeCell ref="D144:F144"/>
+    <mergeCell ref="A145:C145"/>
+    <mergeCell ref="D145:F145"/>
+    <mergeCell ref="A146:C146"/>
+    <mergeCell ref="D146:F146"/>
+    <mergeCell ref="A147:C147"/>
+    <mergeCell ref="D147:F147"/>
+    <mergeCell ref="A148:C148"/>
+    <mergeCell ref="D148:F148"/>
+    <mergeCell ref="A139:C139"/>
+    <mergeCell ref="D139:F139"/>
+    <mergeCell ref="A140:C140"/>
+    <mergeCell ref="D140:F140"/>
+    <mergeCell ref="A141:C141"/>
+    <mergeCell ref="D141:F141"/>
+    <mergeCell ref="A142:C142"/>
+    <mergeCell ref="D142:F142"/>
+    <mergeCell ref="A143:C143"/>
+    <mergeCell ref="D143:F143"/>
+    <mergeCell ref="A134:C134"/>
+    <mergeCell ref="D134:F134"/>
+    <mergeCell ref="A135:C135"/>
+    <mergeCell ref="D135:F135"/>
+    <mergeCell ref="A136:C136"/>
+    <mergeCell ref="D136:F136"/>
+    <mergeCell ref="A137:C137"/>
+    <mergeCell ref="D137:F137"/>
+    <mergeCell ref="A138:C138"/>
+    <mergeCell ref="D138:F138"/>
+    <mergeCell ref="A129:C129"/>
+    <mergeCell ref="D129:F129"/>
+    <mergeCell ref="A130:C130"/>
+    <mergeCell ref="D130:F130"/>
+    <mergeCell ref="A131:C131"/>
+    <mergeCell ref="D131:F131"/>
+    <mergeCell ref="A132:C132"/>
+    <mergeCell ref="D132:F132"/>
+    <mergeCell ref="A133:C133"/>
+    <mergeCell ref="D133:F133"/>
+    <mergeCell ref="A124:C124"/>
+    <mergeCell ref="D124:F124"/>
+    <mergeCell ref="A125:C125"/>
+    <mergeCell ref="D125:F125"/>
+    <mergeCell ref="A126:C126"/>
+    <mergeCell ref="D126:F126"/>
+    <mergeCell ref="A127:C127"/>
+    <mergeCell ref="D127:F127"/>
+    <mergeCell ref="A128:C128"/>
+    <mergeCell ref="D128:F128"/>
+    <mergeCell ref="A119:C119"/>
+    <mergeCell ref="D119:F119"/>
+    <mergeCell ref="A120:C120"/>
+    <mergeCell ref="D120:F120"/>
+    <mergeCell ref="A121:C121"/>
+    <mergeCell ref="D121:F121"/>
+    <mergeCell ref="A122:C122"/>
+    <mergeCell ref="D122:F122"/>
+    <mergeCell ref="A123:C123"/>
+    <mergeCell ref="D123:F123"/>
+    <mergeCell ref="A114:C114"/>
+    <mergeCell ref="D114:F114"/>
+    <mergeCell ref="A115:C115"/>
+    <mergeCell ref="D115:F115"/>
+    <mergeCell ref="A116:C116"/>
+    <mergeCell ref="D116:F116"/>
+    <mergeCell ref="A117:C117"/>
+    <mergeCell ref="D117:F117"/>
+    <mergeCell ref="A118:C118"/>
+    <mergeCell ref="D118:F118"/>
+    <mergeCell ref="A109:C109"/>
+    <mergeCell ref="D109:F109"/>
+    <mergeCell ref="A110:C110"/>
+    <mergeCell ref="D110:F110"/>
+    <mergeCell ref="A111:C111"/>
+    <mergeCell ref="D111:F111"/>
+    <mergeCell ref="A112:C112"/>
+    <mergeCell ref="D112:F112"/>
+    <mergeCell ref="A113:C113"/>
+    <mergeCell ref="D113:F113"/>
+    <mergeCell ref="A104:C104"/>
+    <mergeCell ref="D104:F104"/>
+    <mergeCell ref="A105:C105"/>
+    <mergeCell ref="D105:F105"/>
+    <mergeCell ref="A106:C106"/>
+    <mergeCell ref="D106:F106"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="D107:F107"/>
+    <mergeCell ref="A108:C108"/>
+    <mergeCell ref="D108:F108"/>
+    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="D99:F99"/>
+    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="D100:F100"/>
+    <mergeCell ref="A101:C101"/>
+    <mergeCell ref="D101:F101"/>
+    <mergeCell ref="A102:C102"/>
+    <mergeCell ref="D102:F102"/>
+    <mergeCell ref="A103:C103"/>
+    <mergeCell ref="D103:F103"/>
+    <mergeCell ref="A94:C94"/>
+    <mergeCell ref="D94:F94"/>
+    <mergeCell ref="A95:C95"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="A96:C96"/>
+    <mergeCell ref="D96:F96"/>
+    <mergeCell ref="A97:C97"/>
+    <mergeCell ref="D97:F97"/>
+    <mergeCell ref="A98:C98"/>
+    <mergeCell ref="D98:F98"/>
+    <mergeCell ref="A89:C89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="A90:C90"/>
+    <mergeCell ref="D90:F90"/>
+    <mergeCell ref="A91:C91"/>
+    <mergeCell ref="D91:F91"/>
+    <mergeCell ref="A92:C92"/>
+    <mergeCell ref="D92:F92"/>
+    <mergeCell ref="A93:C93"/>
+    <mergeCell ref="D93:F93"/>
+    <mergeCell ref="A84:C84"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="A85:C85"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="A86:C86"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="A87:C87"/>
+    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="A88:C88"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="A79:C79"/>
+    <mergeCell ref="D79:F79"/>
+    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="A81:C81"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="A82:C82"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="A83:C83"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="A74:C74"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="A76:C76"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="A77:C77"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="A78:C78"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="A70:C70"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="A73:C73"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="A66:C66"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="1" top="0.75" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
